--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-16.xlsx
@@ -1354,7 +1354,7 @@
     <t>Universitario de Deportes</t>
   </si>
   <si>
-    <t>2026-08-14 00:30:33</t>
+    <t>2026-08-14 02:54:26</t>
   </si>
 </sst>
 </file>
@@ -1954,7 +1954,7 @@
         <v>1.82</v>
       </c>
       <c r="H2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>5.7</v>
@@ -2005,7 +2005,7 @@
         <v>16</v>
       </c>
       <c r="Y2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z2">
         <v>48</v>
@@ -2101,7 +2101,7 @@
         <v>5.4</v>
       </c>
       <c r="BE2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF2">
         <v>9.6</v>
@@ -2190,22 +2190,22 @@
         <v>308</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="G3">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="H3">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="I3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J3">
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -2214,16 +2214,16 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
         <v>1.31</v>
       </c>
       <c r="P3">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="Q3">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="R3">
         <v>1.28</v>
@@ -2238,10 +2238,10 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -2435,10 +2435,10 @@
         <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I4">
         <v>4.1</v>
@@ -2462,13 +2462,13 @@
         <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
         <v>3.6</v>
@@ -2483,7 +2483,7 @@
         <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -2707,19 +2707,19 @@
         <v>1.44</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="V5">
         <v>1.76</v>
@@ -2728,7 +2728,7 @@
         <v>1.28</v>
       </c>
       <c r="X5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y5">
         <v>6.6</v>
@@ -2761,7 +2761,7 @@
         <v>32</v>
       </c>
       <c r="AI5">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
         <v>120</v>
@@ -2776,7 +2776,7 @@
         <v>280</v>
       </c>
       <c r="AN5">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AO5">
         <v>42</v>
@@ -2821,7 +2821,7 @@
         <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>70</v>
+        <v>10.5</v>
       </c>
       <c r="BD5">
         <v>10.5</v>
@@ -2919,19 +2919,19 @@
         <v>1.2</v>
       </c>
       <c r="G6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I6">
         <v>25</v>
       </c>
       <c r="J6">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L6">
         <v>1.21</v>
@@ -2952,13 +2952,13 @@
         <v>1.67</v>
       </c>
       <c r="R6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S6">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T6">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="U6">
         <v>1.64</v>
@@ -2967,7 +2967,7 @@
         <v>1.04</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="X6">
         <v>26</v>
@@ -2982,7 +2982,7 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC6">
         <v>17</v>
@@ -3009,7 +3009,7 @@
         <v>10</v>
       </c>
       <c r="AK6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL6">
         <v>75</v>
@@ -3024,58 +3024,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>15.5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR6">
+        <v>6.6</v>
+      </c>
+      <c r="AS6">
+        <v>6.6</v>
+      </c>
+      <c r="AT6">
+        <v>3.75</v>
+      </c>
+      <c r="AU6">
+        <v>4.8</v>
+      </c>
+      <c r="AV6">
         <v>6.2</v>
       </c>
-      <c r="AS6">
-        <v>6.4</v>
-      </c>
-      <c r="AT6">
+      <c r="AW6">
         <v>6.6</v>
       </c>
-      <c r="AU6">
-        <v>13.5</v>
-      </c>
-      <c r="AV6">
+      <c r="AX6">
+        <v>3.45</v>
+      </c>
+      <c r="AY6">
+        <v>4.4</v>
+      </c>
+      <c r="AZ6">
         <v>6</v>
       </c>
-      <c r="AW6">
-        <v>6.4</v>
-      </c>
-      <c r="AX6">
-        <v>5.9</v>
-      </c>
-      <c r="AY6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6">
-        <v>5.7</v>
-      </c>
       <c r="BA6">
+        <v>6.6</v>
+      </c>
+      <c r="BB6">
+        <v>4</v>
+      </c>
+      <c r="BC6">
+        <v>5</v>
+      </c>
+      <c r="BD6">
         <v>6.2</v>
       </c>
-      <c r="BB6">
-        <v>7.2</v>
-      </c>
-      <c r="BC6">
-        <v>11.5</v>
-      </c>
-      <c r="BD6">
-        <v>5.9</v>
-      </c>
       <c r="BE6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF6">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="BG6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -3158,52 +3158,52 @@
         <v>312</v>
       </c>
       <c r="F7">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G7">
         <v>2.38</v>
       </c>
       <c r="H7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J7">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="O7">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P7">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R7">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="S7">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="T7">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="U7">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
         <v>1.47</v>
@@ -3215,109 +3215,109 @@
         <v>40</v>
       </c>
       <c r="Y7">
+        <v>22</v>
+      </c>
+      <c r="Z7">
         <v>29</v>
       </c>
-      <c r="Z7">
-        <v>38</v>
-      </c>
       <c r="AA7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB7">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AC7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AE7">
         <v>38</v>
       </c>
       <c r="AF7">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AG7">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AH7">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AI7">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AJ7">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AL7">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AM7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN7">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AO7">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AP7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AQ7">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR7">
         <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>3.1</v>
+        <v>30</v>
       </c>
       <c r="AT7">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AU7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW7">
         <v>17.5</v>
       </c>
       <c r="AX7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY7">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA7">
         <v>18.5</v>
       </c>
       <c r="BB7">
-        <v>3.05</v>
+        <v>20</v>
       </c>
       <c r="BC7">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD7">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BE7">
-        <v>3.1</v>
+        <v>28</v>
       </c>
       <c r="BF7">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BG7">
-        <v>2.82</v>
+        <v>13.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3403,10 +3403,10 @@
         <v>1.76</v>
       </c>
       <c r="G8">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H8">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I8">
         <v>5</v>
@@ -3415,34 +3415,34 @@
         <v>4.1</v>
       </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P8">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S8">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="T8">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="U8">
         <v>2.34</v>
@@ -3451,49 +3451,49 @@
         <v>1.25</v>
       </c>
       <c r="W8">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X8">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Y8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z8">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE8">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AF8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
+        <v>18</v>
+      </c>
+      <c r="AI8">
+        <v>55</v>
+      </c>
+      <c r="AJ8">
         <v>20</v>
       </c>
-      <c r="AI8">
-        <v>200</v>
-      </c>
-      <c r="AJ8">
-        <v>23</v>
-      </c>
       <c r="AK8">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AL8">
         <v>46</v>
@@ -3502,55 +3502,55 @@
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AO8">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP8">
+        <v>19</v>
+      </c>
+      <c r="AQ8">
         <v>18</v>
       </c>
-      <c r="AQ8">
-        <v>17.5</v>
-      </c>
       <c r="AR8">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AS8">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AT8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU8">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV8">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW8">
+        <v>36</v>
+      </c>
+      <c r="AX8">
+        <v>11</v>
+      </c>
+      <c r="AY8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8">
+        <v>14.5</v>
+      </c>
+      <c r="BA8">
         <v>27</v>
       </c>
-      <c r="AX8">
-        <v>10</v>
-      </c>
-      <c r="AY8">
-        <v>8.6</v>
-      </c>
-      <c r="AZ8">
-        <v>14</v>
-      </c>
-      <c r="BA8">
-        <v>38</v>
-      </c>
       <c r="BB8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC8">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE8">
         <v>46</v>
@@ -3559,7 +3559,7 @@
         <v>7.2</v>
       </c>
       <c r="BG8">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3657,7 +3657,7 @@
         <v>4.6</v>
       </c>
       <c r="K9">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3669,7 +3669,7 @@
         <v>2.58</v>
       </c>
       <c r="O9">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P9">
         <v>2.58</v>
@@ -3681,7 +3681,7 @@
         <v>1.53</v>
       </c>
       <c r="S9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -3884,22 +3884,22 @@
         <v>315</v>
       </c>
       <c r="F10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G10">
         <v>6</v>
       </c>
       <c r="H10">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="J10">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="K10">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -4126,25 +4126,25 @@
         <v>316</v>
       </c>
       <c r="F11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G11">
         <v>1.54</v>
       </c>
       <c r="H11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I11">
         <v>7.2</v>
       </c>
       <c r="J11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>5.4</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M11">
         <v>1.02</v>
@@ -4153,7 +4153,7 @@
         <v>6.4</v>
       </c>
       <c r="O11">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P11">
         <v>2.84</v>
@@ -4162,22 +4162,22 @@
         <v>1.5</v>
       </c>
       <c r="R11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S11">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="T11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U11">
         <v>2.36</v>
       </c>
       <c r="V11">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W11">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="X11">
         <v>34</v>
@@ -4186,7 +4186,7 @@
         <v>36</v>
       </c>
       <c r="Z11">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -4198,7 +4198,7 @@
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE11">
         <v>1000</v>
@@ -4213,7 +4213,7 @@
         <v>20</v>
       </c>
       <c r="AI11">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="AJ11">
         <v>15.5</v>
@@ -4231,10 +4231,10 @@
         <v>5.3</v>
       </c>
       <c r="AO11">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="AP11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
         <v>25</v>
@@ -4243,7 +4243,7 @@
         <v>42</v>
       </c>
       <c r="AS11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT11">
         <v>11.5</v>
@@ -4261,7 +4261,7 @@
         <v>10</v>
       </c>
       <c r="AY11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
         <v>14.5</v>
@@ -4282,7 +4282,7 @@
         <v>34</v>
       </c>
       <c r="BF11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG11">
         <v>44</v>
@@ -4374,46 +4374,46 @@
         <v>1.86</v>
       </c>
       <c r="H12">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O12">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P12">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q12">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R12">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S12">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T12">
         <v>1.61</v>
       </c>
       <c r="U12">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V12">
         <v>1.25</v>
@@ -4422,28 +4422,28 @@
         <v>2.16</v>
       </c>
       <c r="X12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y12">
         <v>32</v>
       </c>
       <c r="Z12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC12">
         <v>10</v>
       </c>
       <c r="AD12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE12">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF12">
         <v>15</v>
@@ -4455,13 +4455,13 @@
         <v>20</v>
       </c>
       <c r="AI12">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ12">
         <v>28</v>
       </c>
       <c r="AK12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL12">
         <v>32</v>
@@ -4470,13 +4470,13 @@
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO12">
         <v>100</v>
       </c>
       <c r="AP12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12">
         <v>18.5</v>
@@ -4485,7 +4485,7 @@
         <v>26</v>
       </c>
       <c r="AS12">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT12">
         <v>10</v>
@@ -4500,7 +4500,7 @@
         <v>34</v>
       </c>
       <c r="AX12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY12">
         <v>8.800000000000001</v>
@@ -4610,7 +4610,7 @@
         <v>318</v>
       </c>
       <c r="F13">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="G13">
         <v>2.02</v>
@@ -4619,10 +4619,10 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="K13">
         <v>4.1</v>
@@ -4852,16 +4852,16 @@
         <v>319</v>
       </c>
       <c r="F14">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G14">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I14">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J14">
         <v>4.6</v>
@@ -4870,148 +4870,148 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M14">
         <v>1.03</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="O14">
         <v>1.16</v>
       </c>
       <c r="P14">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R14">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S14">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V14">
         <v>1.21</v>
       </c>
       <c r="W14">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y14">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB14">
+        <v>14</v>
+      </c>
+      <c r="AC14">
+        <v>12.5</v>
+      </c>
+      <c r="AD14">
+        <v>26</v>
+      </c>
+      <c r="AE14">
+        <v>65</v>
+      </c>
+      <c r="AF14">
+        <v>15</v>
+      </c>
+      <c r="AG14">
+        <v>10.5</v>
+      </c>
+      <c r="AH14">
         <v>17</v>
       </c>
-      <c r="AC14">
-        <v>1000</v>
-      </c>
-      <c r="AD14">
-        <v>1000</v>
-      </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>1000</v>
-      </c>
-      <c r="AG14">
+      <c r="AI14">
+        <v>60</v>
+      </c>
+      <c r="AJ14">
+        <v>17.5</v>
+      </c>
+      <c r="AK14">
+        <v>15.5</v>
+      </c>
+      <c r="AL14">
+        <v>28</v>
+      </c>
+      <c r="AM14">
+        <v>70</v>
+      </c>
+      <c r="AN14">
+        <v>5.9</v>
+      </c>
+      <c r="AO14">
+        <v>48</v>
+      </c>
+      <c r="AP14">
+        <v>7.2</v>
+      </c>
+      <c r="AQ14">
+        <v>7</v>
+      </c>
+      <c r="AR14">
+        <v>8</v>
+      </c>
+      <c r="AS14">
+        <v>8.6</v>
+      </c>
+      <c r="AT14">
+        <v>12</v>
+      </c>
+      <c r="AU14">
+        <v>10.5</v>
+      </c>
+      <c r="AV14">
+        <v>19.5</v>
+      </c>
+      <c r="AW14">
+        <v>8</v>
+      </c>
+      <c r="AX14">
         <v>11.5</v>
       </c>
-      <c r="AH14">
-        <v>20</v>
-      </c>
-      <c r="AI14">
-        <v>1000</v>
-      </c>
-      <c r="AJ14">
+      <c r="AY14">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14">
+        <v>15</v>
+      </c>
+      <c r="BA14">
+        <v>8</v>
+      </c>
+      <c r="BB14">
+        <v>15</v>
+      </c>
+      <c r="BC14">
+        <v>13</v>
+      </c>
+      <c r="BD14">
         <v>21</v>
       </c>
-      <c r="AK14">
-        <v>18.5</v>
-      </c>
-      <c r="AL14">
-        <v>1000</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
+      <c r="BE14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF14">
+        <v>5.3</v>
+      </c>
+      <c r="BG14">
         <v>7.6</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>1.84</v>
-      </c>
-      <c r="AQ14">
-        <v>1.75</v>
-      </c>
-      <c r="AR14">
-        <v>1.84</v>
-      </c>
-      <c r="AS14">
-        <v>1.84</v>
-      </c>
-      <c r="AT14">
-        <v>1.66</v>
-      </c>
-      <c r="AU14">
-        <v>1.84</v>
-      </c>
-      <c r="AV14">
-        <v>18</v>
-      </c>
-      <c r="AW14">
-        <v>1.84</v>
-      </c>
-      <c r="AX14">
-        <v>1.84</v>
-      </c>
-      <c r="AY14">
-        <v>9</v>
-      </c>
-      <c r="AZ14">
-        <v>1.68</v>
-      </c>
-      <c r="BA14">
-        <v>1.84</v>
-      </c>
-      <c r="BB14">
-        <v>1.69</v>
-      </c>
-      <c r="BC14">
-        <v>1.67</v>
-      </c>
-      <c r="BD14">
-        <v>17.5</v>
-      </c>
-      <c r="BE14">
-        <v>1.84</v>
-      </c>
-      <c r="BF14">
-        <v>1.48</v>
-      </c>
-      <c r="BG14">
-        <v>1.48</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -5035,10 +5035,10 @@
         <v>6.4</v>
       </c>
       <c r="BO14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP14">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ14">
         <v>6.6</v>
@@ -5056,13 +5056,13 @@
         <v>5.9</v>
       </c>
       <c r="BV14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BW14">
         <v>21</v>
       </c>
       <c r="BX14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY14">
         <v>21</v>
@@ -5094,166 +5094,166 @@
         <v>320</v>
       </c>
       <c r="F15">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I15">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J15">
         <v>4.1</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="O15">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q15">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R15">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="S15">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="T15">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="V15">
         <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y15">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Z15">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA15">
         <v>75</v>
       </c>
       <c r="AB15">
+        <v>16.5</v>
+      </c>
+      <c r="AC15">
+        <v>11</v>
+      </c>
+      <c r="AD15">
+        <v>16</v>
+      </c>
+      <c r="AE15">
+        <v>34</v>
+      </c>
+      <c r="AF15">
+        <v>19</v>
+      </c>
+      <c r="AG15">
+        <v>12</v>
+      </c>
+      <c r="AH15">
+        <v>15.5</v>
+      </c>
+      <c r="AI15">
+        <v>36</v>
+      </c>
+      <c r="AJ15">
+        <v>29</v>
+      </c>
+      <c r="AK15">
         <v>21</v>
       </c>
-      <c r="AC15">
+      <c r="AL15">
+        <v>27</v>
+      </c>
+      <c r="AM15">
+        <v>60</v>
+      </c>
+      <c r="AN15">
+        <v>11</v>
+      </c>
+      <c r="AO15">
+        <v>21</v>
+      </c>
+      <c r="AP15">
+        <v>6.4</v>
+      </c>
+      <c r="AQ15">
+        <v>17.5</v>
+      </c>
+      <c r="AR15">
+        <v>6.4</v>
+      </c>
+      <c r="AS15">
+        <v>7</v>
+      </c>
+      <c r="AT15">
         <v>13</v>
       </c>
-      <c r="AD15">
-        <v>20</v>
-      </c>
-      <c r="AE15">
-        <v>46</v>
-      </c>
-      <c r="AF15">
-        <v>25</v>
-      </c>
-      <c r="AG15">
-        <v>13.5</v>
-      </c>
-      <c r="AH15">
-        <v>20</v>
-      </c>
-      <c r="AI15">
-        <v>48</v>
-      </c>
-      <c r="AJ15">
-        <v>38</v>
-      </c>
-      <c r="AK15">
-        <v>28</v>
-      </c>
-      <c r="AL15">
-        <v>36</v>
-      </c>
-      <c r="AM15">
-        <v>70</v>
-      </c>
-      <c r="AN15">
-        <v>12</v>
-      </c>
-      <c r="AO15">
-        <v>28</v>
-      </c>
-      <c r="AP15">
-        <v>3.05</v>
-      </c>
-      <c r="AQ15">
-        <v>14.5</v>
-      </c>
-      <c r="AR15">
-        <v>18.5</v>
-      </c>
-      <c r="AS15">
-        <v>3</v>
-      </c>
-      <c r="AT15">
-        <v>11.5</v>
-      </c>
       <c r="AU15">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW15">
-        <v>2.92</v>
+        <v>6.4</v>
       </c>
       <c r="AX15">
+        <v>15</v>
+      </c>
+      <c r="AY15">
+        <v>10</v>
+      </c>
+      <c r="AZ15">
         <v>12.5</v>
       </c>
-      <c r="AY15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15">
-        <v>11</v>
-      </c>
       <c r="BA15">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB15">
-        <v>2.88</v>
+        <v>6.2</v>
       </c>
       <c r="BC15">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BD15">
+        <v>21</v>
+      </c>
+      <c r="BE15">
+        <v>7</v>
+      </c>
+      <c r="BF15">
+        <v>8.4</v>
+      </c>
+      <c r="BG15">
         <v>16.5</v>
-      </c>
-      <c r="BE15">
-        <v>2.98</v>
-      </c>
-      <c r="BF15">
-        <v>7.6</v>
-      </c>
-      <c r="BG15">
-        <v>14.5</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -5339,7 +5339,7 @@
         <v>3.45</v>
       </c>
       <c r="G16">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H16">
         <v>2.24</v>
@@ -5348,34 +5348,34 @@
         <v>2.42</v>
       </c>
       <c r="J16">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L16">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N16">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="O16">
         <v>1.37</v>
       </c>
       <c r="P16">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q16">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="R16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S16">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -5387,7 +5387,7 @@
         <v>1.7</v>
       </c>
       <c r="W16">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -6307,10 +6307,10 @@
         <v>2.44</v>
       </c>
       <c r="G20">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I20">
         <v>3.65</v>
@@ -6334,7 +6334,7 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="Q20">
         <v>2.44</v>
@@ -8255,7 +8255,7 @@
         <v>3.5</v>
       </c>
       <c r="K28">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -8270,10 +8270,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q28">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -8482,22 +8482,22 @@
         <v>334</v>
       </c>
       <c r="F29">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G29">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="H29">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="I29">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="J29">
         <v>3.6</v>
       </c>
       <c r="K29">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>2.04</v>
       </c>
       <c r="Q29">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8978,7 +8978,7 @@
         <v>5.4</v>
       </c>
       <c r="J31">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K31">
         <v>5.7</v>
@@ -8996,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q31">
         <v>1.43</v>
@@ -9220,7 +9220,7 @@
         <v>2.96</v>
       </c>
       <c r="J32">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K32">
         <v>4.1</v>
@@ -9462,7 +9462,7 @@
         <v>3.55</v>
       </c>
       <c r="J33">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K33">
         <v>4.1</v>
@@ -9704,7 +9704,7 @@
         <v>5.7</v>
       </c>
       <c r="J34">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K34">
         <v>4.7</v>
@@ -9722,10 +9722,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q34">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9964,10 +9964,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="Q35">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -10176,16 +10176,16 @@
         <v>341</v>
       </c>
       <c r="F36">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G36">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H36">
         <v>4</v>
       </c>
       <c r="I36">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J36">
         <v>4.1</v>
@@ -10427,13 +10427,13 @@
         <v>2.38</v>
       </c>
       <c r="I37">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="J37">
         <v>3.5</v>
       </c>
       <c r="K37">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -10448,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q37">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -10663,13 +10663,13 @@
         <v>1.41</v>
       </c>
       <c r="G38">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H38">
         <v>7.4</v>
       </c>
       <c r="I38">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J38">
         <v>5.6</v>
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -11386,7 +11386,7 @@
         <v>346</v>
       </c>
       <c r="F41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G41">
         <v>1.3</v>
@@ -11661,7 +11661,7 @@
         <v>3.25</v>
       </c>
       <c r="Q42">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11870,16 +11870,16 @@
         <v>348</v>
       </c>
       <c r="F43">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G43">
         <v>3.8</v>
       </c>
       <c r="H43">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I43">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J43">
         <v>3.7</v>
@@ -12850,7 +12850,7 @@
         <v>2.76</v>
       </c>
       <c r="J47">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K47">
         <v>4.7</v>
@@ -13328,13 +13328,13 @@
         <v>1.38</v>
       </c>
       <c r="H49">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I49">
         <v>13</v>
       </c>
       <c r="J49">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K49">
         <v>7.4</v>
@@ -13355,7 +13355,7 @@
         <v>2.68</v>
       </c>
       <c r="Q49">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -15745,7 +15745,7 @@
         <v>3.55</v>
       </c>
       <c r="G59">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H59">
         <v>2.04</v>
@@ -15757,7 +15757,7 @@
         <v>3.45</v>
       </c>
       <c r="K59">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -15772,10 +15772,10 @@
         <v>0</v>
       </c>
       <c r="P59">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="Q59">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -15984,7 +15984,7 @@
         <v>365</v>
       </c>
       <c r="F60">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G60">
         <v>3.45</v>
@@ -15999,7 +15999,7 @@
         <v>3.45</v>
       </c>
       <c r="K60">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -16017,7 +16017,7 @@
         <v>1.79</v>
       </c>
       <c r="Q60">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -16471,10 +16471,10 @@
         <v>3.95</v>
       </c>
       <c r="G62">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H62">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I62">
         <v>2</v>
@@ -16498,7 +16498,7 @@
         <v>0</v>
       </c>
       <c r="P62">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q62">
         <v>1.66</v>
@@ -16952,16 +16952,16 @@
         <v>369</v>
       </c>
       <c r="F64">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G64">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H64">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I64">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J64">
         <v>3.7</v>
@@ -16982,7 +16982,7 @@
         <v>0</v>
       </c>
       <c r="P64">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="Q64">
         <v>1.57</v>
@@ -17194,7 +17194,7 @@
         <v>370</v>
       </c>
       <c r="F65">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G65">
         <v>4.4</v>
@@ -17436,13 +17436,13 @@
         <v>371</v>
       </c>
       <c r="F66">
-        <v>1.55</v>
+        <v>2.68</v>
       </c>
       <c r="G66">
         <v>3.2</v>
       </c>
       <c r="H66">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="I66">
         <v>2.8</v>
@@ -17451,7 +17451,7 @@
         <v>3.6</v>
       </c>
       <c r="K66">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -17929,7 +17929,7 @@
         <v>6.4</v>
       </c>
       <c r="I68">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J68">
         <v>5.1</v>
@@ -17950,7 +17950,7 @@
         <v>0</v>
       </c>
       <c r="P68">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q68">
         <v>1.43</v>
@@ -18655,10 +18655,10 @@
         <v>4.2</v>
       </c>
       <c r="I71">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J71">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K71">
         <v>3.6</v>
@@ -18927,7 +18927,7 @@
         <v>1.44</v>
       </c>
       <c r="S72">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T72">
         <v>1.7</v>
@@ -18993,7 +18993,7 @@
         <v>32</v>
       </c>
       <c r="AO72">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP72">
         <v>14.5</v>
@@ -19005,7 +19005,7 @@
         <v>14</v>
       </c>
       <c r="AS72">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AT72">
         <v>13</v>
@@ -19020,7 +19020,7 @@
         <v>21</v>
       </c>
       <c r="AX72">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY72">
         <v>13</v>
@@ -19029,7 +19029,7 @@
         <v>14.5</v>
       </c>
       <c r="BA72">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BB72">
         <v>28</v>
@@ -19038,13 +19038,13 @@
         <v>30</v>
       </c>
       <c r="BD72">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BE72">
         <v>34</v>
       </c>
       <c r="BF72">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BG72">
         <v>14</v>
@@ -20101,13 +20101,13 @@
         <v>2.64</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H77">
         <v>2.66</v>
       </c>
       <c r="I77">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J77">
         <v>3.4</v>
@@ -20128,7 +20128,7 @@
         <v>0</v>
       </c>
       <c r="P77">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="Q77">
         <v>1.89</v>
@@ -20349,7 +20349,7 @@
         <v>3.15</v>
       </c>
       <c r="I78">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J78">
         <v>3.85</v>
@@ -20370,7 +20370,7 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q78">
         <v>1.18</v>
@@ -20824,7 +20824,7 @@
         <v>385</v>
       </c>
       <c r="F80">
-        <v>2.88</v>
+        <v>1.72</v>
       </c>
       <c r="G80">
         <v>3.5</v>
@@ -21308,13 +21308,13 @@
         <v>387</v>
       </c>
       <c r="F82">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G82">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H82">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I82">
         <v>2.42</v>
@@ -21335,7 +21335,7 @@
         <v>4.3</v>
       </c>
       <c r="O82">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P82">
         <v>2.14</v>
@@ -21377,7 +21377,7 @@
         <v>15</v>
       </c>
       <c r="AC82">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD82">
         <v>11.5</v>
@@ -21389,13 +21389,13 @@
         <v>24</v>
       </c>
       <c r="AG82">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH82">
         <v>16</v>
       </c>
       <c r="AI82">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ82">
         <v>60</v>
@@ -21404,7 +21404,7 @@
         <v>34</v>
       </c>
       <c r="AL82">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM82">
         <v>85</v>
@@ -21416,7 +21416,7 @@
         <v>16.5</v>
       </c>
       <c r="AP82">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ82">
         <v>10.5</v>
@@ -21443,13 +21443,13 @@
         <v>20</v>
       </c>
       <c r="AY82">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ82">
         <v>14</v>
       </c>
       <c r="BA82">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB82">
         <v>40</v>
@@ -21792,7 +21792,7 @@
         <v>389</v>
       </c>
       <c r="F84">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G84">
         <v>3.5</v>
@@ -21801,7 +21801,7 @@
         <v>2.26</v>
       </c>
       <c r="I84">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J84">
         <v>3.3</v>
@@ -23005,16 +23005,16 @@
         <v>2.82</v>
       </c>
       <c r="G89">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H89">
         <v>2.66</v>
       </c>
       <c r="I89">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="J89">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="K89">
         <v>3.5</v>
@@ -23731,7 +23731,7 @@
         <v>1.28</v>
       </c>
       <c r="G92">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H92">
         <v>13</v>
@@ -23761,7 +23761,7 @@
         <v>1.85</v>
       </c>
       <c r="Q92">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>1.76</v>
       </c>
       <c r="H96">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I96">
         <v>8.6</v>
@@ -24711,7 +24711,7 @@
         <v>3.9</v>
       </c>
       <c r="K96">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -24783,13 +24783,13 @@
         <v>21</v>
       </c>
       <c r="AI96">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ96">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK96">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL96">
         <v>38</v>
@@ -24804,58 +24804,58 @@
         <v>90</v>
       </c>
       <c r="AP96">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ96">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AR96">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS96">
+        <v>5.9</v>
+      </c>
+      <c r="AT96">
+        <v>4</v>
+      </c>
+      <c r="AU96">
+        <v>3.85</v>
+      </c>
+      <c r="AV96">
+        <v>5</v>
+      </c>
+      <c r="AW96">
         <v>5.7</v>
       </c>
-      <c r="AT96">
-        <v>3.95</v>
-      </c>
-      <c r="AU96">
-        <v>3.75</v>
-      </c>
-      <c r="AV96">
-        <v>4.8</v>
-      </c>
-      <c r="AW96">
-        <v>5.5</v>
-      </c>
       <c r="AX96">
+        <v>4.1</v>
+      </c>
+      <c r="AY96">
         <v>4</v>
       </c>
-      <c r="AY96">
-        <v>3.95</v>
-      </c>
       <c r="AZ96">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA96">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB96">
         <v>4.4</v>
       </c>
       <c r="BC96">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD96">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE96">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF96">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BG96">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH96">
         <v>0</v>
@@ -25183,10 +25183,10 @@
         <v>1.48</v>
       </c>
       <c r="G98">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H98">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="I98">
         <v>11</v>
@@ -25195,7 +25195,7 @@
         <v>4.3</v>
       </c>
       <c r="K98">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -25422,19 +25422,19 @@
         <v>404</v>
       </c>
       <c r="F99">
+        <v>2.64</v>
+      </c>
+      <c r="G99">
+        <v>3.15</v>
+      </c>
+      <c r="H99">
         <v>2.7</v>
       </c>
-      <c r="G99">
-        <v>2.9</v>
-      </c>
-      <c r="H99">
-        <v>2.72</v>
-      </c>
       <c r="I99">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="J99">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K99">
         <v>3.65</v>
@@ -25679,7 +25679,7 @@
         <v>3.25</v>
       </c>
       <c r="K100">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -26148,7 +26148,7 @@
         <v>407</v>
       </c>
       <c r="F102">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G102">
         <v>2.18</v>
@@ -26178,7 +26178,7 @@
         <v>1.45</v>
       </c>
       <c r="P102">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q102">
         <v>2.34</v>
@@ -26193,7 +26193,7 @@
         <v>2.04</v>
       </c>
       <c r="U102">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V102">
         <v>0</v>
@@ -26208,10 +26208,10 @@
         <v>12.5</v>
       </c>
       <c r="Z102">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA102">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB102">
         <v>7.8</v>
@@ -26232,7 +26232,7 @@
         <v>11</v>
       </c>
       <c r="AH102">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI102">
         <v>90</v>
@@ -26247,13 +26247,13 @@
         <v>60</v>
       </c>
       <c r="AM102">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AN102">
         <v>23</v>
       </c>
       <c r="AO102">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP102">
         <v>9.4</v>
@@ -26268,7 +26268,7 @@
         <v>36</v>
       </c>
       <c r="AT102">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU102">
         <v>6.8</v>
@@ -26277,7 +26277,7 @@
         <v>15.5</v>
       </c>
       <c r="AW102">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AX102">
         <v>11</v>
@@ -26295,7 +26295,7 @@
         <v>18</v>
       </c>
       <c r="BC102">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD102">
         <v>40</v>
@@ -26393,7 +26393,7 @@
         <v>2.44</v>
       </c>
       <c r="G103">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H103">
         <v>3.2</v>
@@ -26647,7 +26647,7 @@
         <v>3.4</v>
       </c>
       <c r="K104">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -26874,7 +26874,7 @@
         <v>410</v>
       </c>
       <c r="F105">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="G105">
         <v>1.77</v>
@@ -26883,13 +26883,13 @@
         <v>5.3</v>
       </c>
       <c r="I105">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="J105">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="K105">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -27842,7 +27842,7 @@
         <v>414</v>
       </c>
       <c r="F109">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G109">
         <v>2.24</v>
@@ -28813,10 +28813,10 @@
         <v>4.4</v>
       </c>
       <c r="G113">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H113">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="I113">
         <v>1.93</v>
@@ -28825,7 +28825,7 @@
         <v>3.7</v>
       </c>
       <c r="K113">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -29539,7 +29539,7 @@
         <v>1.85</v>
       </c>
       <c r="G116">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="H116">
         <v>4.2</v>
@@ -29551,7 +29551,7 @@
         <v>3.4</v>
       </c>
       <c r="K116">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L116">
         <v>0</v>
@@ -29781,19 +29781,19 @@
         <v>2.5</v>
       </c>
       <c r="G117">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H117">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I117">
         <v>3.6</v>
       </c>
       <c r="J117">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K117">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L117">
         <v>0</v>
@@ -30504,13 +30504,13 @@
         <v>425</v>
       </c>
       <c r="F120">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G120">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H120">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I120">
         <v>6.6</v>
@@ -30534,7 +30534,7 @@
         <v>0</v>
       </c>
       <c r="P120">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
       <c r="Q120">
         <v>2.14</v>
@@ -30991,7 +30991,7 @@
         <v>2.2</v>
       </c>
       <c r="G122">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H122">
         <v>3.35</v>
@@ -31000,10 +31000,10 @@
         <v>3.65</v>
       </c>
       <c r="J122">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K122">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L122">
         <v>0</v>
@@ -31472,22 +31472,22 @@
         <v>429</v>
       </c>
       <c r="F124">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="G124">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H124">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="I124">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J124">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K124">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="L124">
         <v>1.01</v>
@@ -31520,10 +31520,10 @@
         <v>1.01</v>
       </c>
       <c r="V124">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W124">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X124">
         <v>1000</v>
@@ -31720,7 +31720,7 @@
         <v>1.36</v>
       </c>
       <c r="H125">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I125">
         <v>11</v>
@@ -31729,7 +31729,7 @@
         <v>5.8</v>
       </c>
       <c r="K125">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L125">
         <v>0</v>
@@ -31744,10 +31744,10 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q125">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -32198,13 +32198,13 @@
         <v>432</v>
       </c>
       <c r="F127">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G127">
         <v>1.94</v>
       </c>
       <c r="H127">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I127">
         <v>5.2</v>
@@ -32213,7 +32213,7 @@
         <v>3.55</v>
       </c>
       <c r="K127">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L127">
         <v>1.01</v>
@@ -32222,22 +32222,22 @@
         <v>1.07</v>
       </c>
       <c r="N127">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O127">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P127">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q127">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R127">
         <v>1.24</v>
       </c>
       <c r="S127">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T127">
         <v>1.01</v>
@@ -32452,7 +32452,7 @@
         <v>5.4</v>
       </c>
       <c r="J128">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="K128">
         <v>3.8</v>
@@ -32930,7 +32930,7 @@
         <v>5.1</v>
       </c>
       <c r="H130">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="I130">
         <v>1.93</v>
@@ -33172,7 +33172,7 @@
         <v>2.14</v>
       </c>
       <c r="H131">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I131">
         <v>5.5</v>
@@ -33656,7 +33656,7 @@
         <v>1.85</v>
       </c>
       <c r="H133">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I133">
         <v>8.199999999999999</v>
@@ -33665,7 +33665,7 @@
         <v>3.75</v>
       </c>
       <c r="K133">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -34140,7 +34140,7 @@
         <v>1.78</v>
       </c>
       <c r="H135">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I135">
         <v>6.2</v>
@@ -34385,13 +34385,13 @@
         <v>4.9</v>
       </c>
       <c r="I136">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J136">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K136">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L136">
         <v>0</v>
@@ -34618,22 +34618,22 @@
         <v>442</v>
       </c>
       <c r="F137">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="G137">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H137">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I137">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J137">
-        <v>3.8</v>
+        <v>2.26</v>
       </c>
       <c r="K137">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -35344,7 +35344,7 @@
         <v>445</v>
       </c>
       <c r="F140">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G140">
         <v>6.4</v>
@@ -35356,7 +35356,7 @@
         <v>1.91</v>
       </c>
       <c r="J140">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K140">
         <v>3.95</v>
@@ -35386,10 +35386,10 @@
         <v>0</v>
       </c>
       <c r="T140">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U140">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V140">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-16.xlsx
@@ -1354,7 +1354,7 @@
     <t>Universitario de Deportes</t>
   </si>
   <si>
-    <t>2026-08-14 02:54:26</t>
+    <t>2026-08-14 05:18:48</t>
   </si>
 </sst>
 </file>
@@ -1951,19 +1951,19 @@
         <v>1.78</v>
       </c>
       <c r="G2">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J2">
         <v>3.75</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1984,43 +1984,43 @@
         <v>1.98</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T2">
         <v>1.89</v>
       </c>
       <c r="U2">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V2">
         <v>1.21</v>
       </c>
       <c r="W2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X2">
         <v>16</v>
       </c>
       <c r="Y2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA2">
         <v>160</v>
       </c>
       <c r="AB2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AC2">
         <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE2">
         <v>90</v>
@@ -2032,13 +2032,13 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI2">
         <v>90</v>
       </c>
       <c r="AJ2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK2">
         <v>23</v>
@@ -2050,10 +2050,10 @@
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
@@ -2062,34 +2062,34 @@
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>5.4</v>
+        <v>29</v>
       </c>
       <c r="AS2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
         <v>16</v>
       </c>
       <c r="AW2">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX2">
         <v>9.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB2">
         <v>14.5</v>
@@ -2098,76 +2098,76 @@
         <v>15</v>
       </c>
       <c r="BD2">
-        <v>5.4</v>
+        <v>28</v>
       </c>
       <c r="BE2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH2">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>446</v>
@@ -2190,22 +2190,22 @@
         <v>308</v>
       </c>
       <c r="F3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G3">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H3">
         <v>3.6</v>
       </c>
       <c r="I3">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -2214,22 +2214,22 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
         <v>1.31</v>
       </c>
       <c r="P3">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q3">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
         <v>1.28</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T3">
         <v>1.66</v>
@@ -2238,10 +2238,10 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -2355,7 +2355,7 @@
         <v>4.2</v>
       </c>
       <c r="BI3">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -2435,19 +2435,19 @@
         <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I4">
         <v>4.1</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -2456,7 +2456,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
         <v>1.36</v>
@@ -2468,7 +2468,7 @@
         <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
         <v>3.6</v>
@@ -2483,7 +2483,7 @@
         <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -2597,7 +2597,7 @@
         <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
@@ -2677,7 +2677,7 @@
         <v>4.1</v>
       </c>
       <c r="G5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H5">
         <v>2.22</v>
@@ -2692,22 +2692,22 @@
         <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="M5">
         <v>1.16</v>
       </c>
       <c r="N5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
         <v>1.64</v>
       </c>
       <c r="P5">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Q5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R5">
         <v>1.14</v>
@@ -2719,7 +2719,7 @@
         <v>2.3</v>
       </c>
       <c r="U5">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V5">
         <v>1.76</v>
@@ -2728,7 +2728,7 @@
         <v>1.28</v>
       </c>
       <c r="X5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y5">
         <v>6.6</v>
@@ -2767,16 +2767,16 @@
         <v>120</v>
       </c>
       <c r="AK5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AL5">
         <v>140</v>
       </c>
       <c r="AM5">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN5">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AO5">
         <v>42</v>
@@ -2815,16 +2815,16 @@
         <v>25</v>
       </c>
       <c r="BA5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC5">
-        <v>10.5</v>
+        <v>70</v>
       </c>
       <c r="BD5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE5">
         <v>10</v>
@@ -2836,7 +2836,7 @@
         <v>28</v>
       </c>
       <c r="BH5">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
         <v>1.01</v>
@@ -2922,16 +2922,16 @@
         <v>1.26</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I6">
         <v>25</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>1.21</v>
@@ -2943,7 +2943,7 @@
         <v>4.5</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
         <v>2.2</v>
@@ -2967,7 +2967,7 @@
         <v>1.04</v>
       </c>
       <c r="W6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X6">
         <v>26</v>
@@ -3009,73 +3009,73 @@
         <v>10</v>
       </c>
       <c r="AK6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM6">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AN6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AQ6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR6">
+        <v>6.8</v>
+      </c>
+      <c r="AS6">
+        <v>7</v>
+      </c>
+      <c r="AT6">
+        <v>3.85</v>
+      </c>
+      <c r="AU6">
+        <v>13.5</v>
+      </c>
+      <c r="AV6">
         <v>6.6</v>
       </c>
-      <c r="AS6">
-        <v>6.6</v>
-      </c>
-      <c r="AT6">
-        <v>3.75</v>
-      </c>
-      <c r="AU6">
-        <v>4.8</v>
-      </c>
-      <c r="AV6">
+      <c r="AW6">
+        <v>7</v>
+      </c>
+      <c r="AX6">
+        <v>3.55</v>
+      </c>
+      <c r="AY6">
+        <v>4.5</v>
+      </c>
+      <c r="AZ6">
         <v>6.2</v>
       </c>
-      <c r="AW6">
-        <v>6.6</v>
-      </c>
-      <c r="AX6">
-        <v>3.45</v>
-      </c>
-      <c r="AY6">
-        <v>4.4</v>
-      </c>
-      <c r="AZ6">
-        <v>6</v>
-      </c>
       <c r="BA6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BD6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF6">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BG6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -3158,19 +3158,19 @@
         <v>312</v>
       </c>
       <c r="F7">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G7">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
       <c r="I7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <v>4.2</v>
@@ -3182,37 +3182,37 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O7">
         <v>1.17</v>
       </c>
       <c r="P7">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="Q7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R7">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S7">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="T7">
         <v>1.47</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X7">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="Y7">
         <v>22</v>
@@ -3221,43 +3221,43 @@
         <v>29</v>
       </c>
       <c r="AA7">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AB7">
         <v>18.5</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF7">
         <v>21</v>
       </c>
       <c r="AG7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI7">
         <v>32</v>
       </c>
       <c r="AJ7">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL7">
         <v>27</v>
       </c>
       <c r="AM7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN7">
         <v>10.5</v>
@@ -3266,16 +3266,16 @@
         <v>16.5</v>
       </c>
       <c r="AP7">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AQ7">
         <v>17.5</v>
       </c>
       <c r="AR7">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT7">
         <v>15</v>
@@ -3284,25 +3284,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX7">
         <v>17</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
         <v>12</v>
       </c>
       <c r="BA7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC7">
         <v>17.5</v>
@@ -3311,10 +3311,10 @@
         <v>21</v>
       </c>
       <c r="BE7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG7">
         <v>13.5</v>
@@ -3341,7 +3341,7 @@
         <v>8</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP7">
         <v>20</v>
@@ -3365,7 +3365,7 @@
         <v>28</v>
       </c>
       <c r="BW7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX7">
         <v>34</v>
@@ -3403,7 +3403,7 @@
         <v>1.76</v>
       </c>
       <c r="G8">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H8">
         <v>4.7</v>
@@ -3418,13 +3418,13 @@
         <v>4.5</v>
       </c>
       <c r="L8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O8">
         <v>1.21</v>
@@ -3436,7 +3436,7 @@
         <v>1.64</v>
       </c>
       <c r="R8">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S8">
         <v>2.62</v>
@@ -3445,13 +3445,13 @@
         <v>1.65</v>
       </c>
       <c r="U8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V8">
         <v>1.25</v>
       </c>
       <c r="W8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X8">
         <v>24</v>
@@ -3460,13 +3460,13 @@
         <v>23</v>
       </c>
       <c r="Z8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC8">
         <v>10.5</v>
@@ -3475,7 +3475,7 @@
         <v>19.5</v>
       </c>
       <c r="AE8">
-        <v>210</v>
+        <v>55</v>
       </c>
       <c r="AF8">
         <v>13</v>
@@ -3484,37 +3484,37 @@
         <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI8">
         <v>55</v>
       </c>
       <c r="AJ8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AK8">
         <v>17.5</v>
       </c>
       <c r="AL8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM8">
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO8">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP8">
+        <v>16.5</v>
+      </c>
+      <c r="AQ8">
         <v>19</v>
       </c>
-      <c r="AQ8">
-        <v>18</v>
-      </c>
       <c r="AR8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS8">
         <v>38</v>
@@ -3523,43 +3523,43 @@
         <v>10</v>
       </c>
       <c r="AU8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV8">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW8">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AX8">
         <v>11</v>
       </c>
       <c r="AY8">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC8">
         <v>14.5</v>
       </c>
       <c r="BD8">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BE8">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BF8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3666,16 +3666,16 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="O9">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="Q9">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="R9">
         <v>1.53</v>
@@ -3884,22 +3884,22 @@
         <v>315</v>
       </c>
       <c r="F10">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I10">
+        <v>2.44</v>
+      </c>
+      <c r="J10">
         <v>2.38</v>
       </c>
-      <c r="J10">
-        <v>2.42</v>
-      </c>
       <c r="K10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>1.51</v>
       </c>
       <c r="G11">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H11">
         <v>6.6</v>
@@ -4153,7 +4153,7 @@
         <v>6.4</v>
       </c>
       <c r="O11">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P11">
         <v>2.84</v>
@@ -4282,7 +4282,7 @@
         <v>34</v>
       </c>
       <c r="BF11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG11">
         <v>44</v>
@@ -4368,19 +4368,19 @@
         <v>317</v>
       </c>
       <c r="F12">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G12">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J12">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>4.2</v>
@@ -4395,7 +4395,7 @@
         <v>5.4</v>
       </c>
       <c r="O12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P12">
         <v>2.46</v>
@@ -4416,13 +4416,13 @@
         <v>2.42</v>
       </c>
       <c r="V12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W12">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y12">
         <v>32</v>
@@ -4440,7 +4440,7 @@
         <v>10</v>
       </c>
       <c r="AD12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE12">
         <v>170</v>
@@ -4461,7 +4461,7 @@
         <v>28</v>
       </c>
       <c r="AK12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL12">
         <v>32</v>
@@ -4485,13 +4485,13 @@
         <v>26</v>
       </c>
       <c r="AS12">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT12">
         <v>10</v>
       </c>
       <c r="AU12">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV12">
         <v>14</v>
@@ -4610,19 +4610,19 @@
         <v>318</v>
       </c>
       <c r="F13">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G13">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H13">
         <v>5</v>
       </c>
       <c r="I13">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="J13">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K13">
         <v>4.1</v>
@@ -4640,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q13">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4852,25 +4852,25 @@
         <v>319</v>
       </c>
       <c r="F14">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G14">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H14">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I14">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J14">
         <v>4.6</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M14">
         <v>1.03</v>
@@ -4879,7 +4879,7 @@
         <v>6.4</v>
       </c>
       <c r="O14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P14">
         <v>2.88</v>
@@ -4891,28 +4891,28 @@
         <v>1.75</v>
       </c>
       <c r="S14">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T14">
         <v>1.59</v>
       </c>
       <c r="U14">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V14">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W14">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA14">
         <v>130</v>
@@ -4921,70 +4921,70 @@
         <v>14</v>
       </c>
       <c r="AC14">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE14">
         <v>65</v>
       </c>
       <c r="AF14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ14">
+        <v>18.5</v>
+      </c>
+      <c r="AK14">
         <v>17.5</v>
       </c>
-      <c r="AK14">
-        <v>15.5</v>
-      </c>
       <c r="AL14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AM14">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AO14">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AP14">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AQ14">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AR14">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AS14">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="AT14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU14">
         <v>10.5</v>
       </c>
       <c r="AV14">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW14">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AX14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY14">
         <v>9.4</v>
@@ -4993,25 +4993,25 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BB14">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD14">
         <v>21</v>
       </c>
       <c r="BE14">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BF14">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG14">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -5035,10 +5035,10 @@
         <v>6.4</v>
       </c>
       <c r="BO14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ14">
         <v>6.6</v>
@@ -5056,13 +5056,13 @@
         <v>5.9</v>
       </c>
       <c r="BV14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW14">
         <v>21</v>
       </c>
       <c r="BX14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY14">
         <v>21</v>
@@ -5094,7 +5094,7 @@
         <v>320</v>
       </c>
       <c r="F15">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G15">
         <v>2.18</v>
@@ -5103,7 +5103,7 @@
         <v>3.3</v>
       </c>
       <c r="I15">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J15">
         <v>4.1</v>
@@ -5121,16 +5121,16 @@
         <v>6.2</v>
       </c>
       <c r="O15">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P15">
         <v>2.76</v>
       </c>
       <c r="Q15">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R15">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S15">
         <v>2.32</v>
@@ -5142,79 +5142,79 @@
         <v>2.76</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W15">
         <v>1.84</v>
       </c>
       <c r="X15">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Y15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Z15">
         <v>32</v>
       </c>
       <c r="AA15">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AB15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE15">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AF15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AG15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH15">
         <v>15.5</v>
       </c>
       <c r="AI15">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AJ15">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AK15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL15">
         <v>27</v>
       </c>
       <c r="AM15">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AN15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO15">
         <v>21</v>
       </c>
       <c r="AP15">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AQ15">
         <v>17.5</v>
       </c>
       <c r="AR15">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="AS15">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AT15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU15">
         <v>9.199999999999999</v>
@@ -5223,7 +5223,7 @@
         <v>12.5</v>
       </c>
       <c r="AW15">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="AX15">
         <v>15</v>
@@ -5232,13 +5232,13 @@
         <v>10</v>
       </c>
       <c r="AZ15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA15">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BB15">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BC15">
         <v>16</v>
@@ -5247,13 +5247,13 @@
         <v>21</v>
       </c>
       <c r="BE15">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BF15">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG15">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -5345,13 +5345,13 @@
         <v>2.24</v>
       </c>
       <c r="I16">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="J16">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K16">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -5369,13 +5369,13 @@
         <v>1.72</v>
       </c>
       <c r="Q16">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R16">
         <v>1.08</v>
       </c>
       <c r="S16">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -5384,7 +5384,7 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W16">
         <v>1.34</v>
@@ -6304,22 +6304,22 @@
         <v>325</v>
       </c>
       <c r="F20">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G20">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I20">
         <v>3.65</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K20">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -6334,10 +6334,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q20">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>3.1</v>
       </c>
       <c r="H22">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I22">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="J22">
         <v>3.6</v>
@@ -8243,19 +8243,19 @@
         <v>2.6</v>
       </c>
       <c r="G28">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="H28">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I28">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J28">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K28">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -8273,7 +8273,7 @@
         <v>2.06</v>
       </c>
       <c r="Q28">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -8485,7 +8485,7 @@
         <v>3.6</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H29">
         <v>2.08</v>
@@ -8512,7 +8512,7 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q29">
         <v>1.84</v>
@@ -8966,22 +8966,22 @@
         <v>336</v>
       </c>
       <c r="F31">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="G31">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="H31">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I31">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J31">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K31">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -9208,19 +9208,19 @@
         <v>337</v>
       </c>
       <c r="F32">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G32">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H32">
         <v>2.74</v>
       </c>
       <c r="I32">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J32">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K32">
         <v>4.1</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q32">
         <v>1.63</v>
@@ -9692,7 +9692,7 @@
         <v>339</v>
       </c>
       <c r="F34">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G34">
         <v>1.83</v>
@@ -9701,7 +9701,7 @@
         <v>4.4</v>
       </c>
       <c r="I34">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J34">
         <v>4.2</v>
@@ -9722,10 +9722,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q34">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>340</v>
       </c>
       <c r="F35">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="G35">
         <v>1.63</v>
@@ -9943,13 +9943,13 @@
         <v>5.8</v>
       </c>
       <c r="I35">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J35">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K35">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9964,10 +9964,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -10185,7 +10185,7 @@
         <v>4</v>
       </c>
       <c r="I36">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J36">
         <v>4.1</v>
@@ -10206,7 +10206,7 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q36">
         <v>1.51</v>
@@ -10660,16 +10660,16 @@
         <v>343</v>
       </c>
       <c r="F38">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G38">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H38">
         <v>7.4</v>
       </c>
       <c r="I38">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J38">
         <v>5.6</v>
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q38">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -11174,10 +11174,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="Q40">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -11392,16 +11392,16 @@
         <v>1.3</v>
       </c>
       <c r="H41">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I41">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J41">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K41">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -11416,10 +11416,10 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="Q41">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -11634,16 +11634,16 @@
         <v>1.45</v>
       </c>
       <c r="H42">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I42">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J42">
         <v>5.5</v>
       </c>
       <c r="K42">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -11870,19 +11870,19 @@
         <v>348</v>
       </c>
       <c r="F43">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="G43">
         <v>3.8</v>
       </c>
       <c r="H43">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I43">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J43">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K43">
         <v>3.8</v>
@@ -11915,7 +11915,7 @@
         <v>1.66</v>
       </c>
       <c r="U43">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -11999,7 +11999,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW43">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX43">
         <v>18</v>
@@ -12118,13 +12118,13 @@
         <v>2.9</v>
       </c>
       <c r="H44">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I44">
         <v>2.48</v>
       </c>
       <c r="J44">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K44">
         <v>4.7</v>
@@ -12142,10 +12142,10 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q44">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -12838,22 +12838,22 @@
         <v>352</v>
       </c>
       <c r="F47">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G47">
         <v>2.92</v>
       </c>
       <c r="H47">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I47">
         <v>2.76</v>
       </c>
       <c r="J47">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K47">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -13083,16 +13083,16 @@
         <v>1.46</v>
       </c>
       <c r="G48">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H48">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I48">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J48">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K48">
         <v>5.3</v>
@@ -13325,13 +13325,13 @@
         <v>1.32</v>
       </c>
       <c r="G49">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H49">
         <v>9.6</v>
       </c>
       <c r="I49">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J49">
         <v>5.9</v>
@@ -13352,10 +13352,10 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="Q49">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -14048,22 +14048,22 @@
         <v>357</v>
       </c>
       <c r="F52">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G52">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H52">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I52">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J52">
         <v>3.3</v>
       </c>
       <c r="K52">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -14078,7 +14078,7 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q52">
         <v>2.08</v>
@@ -14535,16 +14535,16 @@
         <v>2.72</v>
       </c>
       <c r="G54">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H54">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I54">
         <v>2.84</v>
       </c>
       <c r="J54">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K54">
         <v>3.75</v>
@@ -14565,7 +14565,7 @@
         <v>1.74</v>
       </c>
       <c r="Q54">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14774,22 +14774,22 @@
         <v>360</v>
       </c>
       <c r="F55">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G55">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H55">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I55">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J55">
         <v>3.1</v>
       </c>
       <c r="K55">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -15261,16 +15261,16 @@
         <v>4.1</v>
       </c>
       <c r="G57">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H57">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I57">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="J57">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K57">
         <v>4.7</v>
@@ -15288,10 +15288,10 @@
         <v>0</v>
       </c>
       <c r="P57">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="Q57">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -15745,10 +15745,10 @@
         <v>3.55</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H59">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I59">
         <v>2.24</v>
@@ -15757,7 +15757,7 @@
         <v>3.45</v>
       </c>
       <c r="K59">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -15775,7 +15775,7 @@
         <v>1.25</v>
       </c>
       <c r="Q59">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -15996,7 +15996,7 @@
         <v>2.52</v>
       </c>
       <c r="J60">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K60">
         <v>3.65</v>
@@ -16014,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q60">
         <v>1.79</v>
@@ -16468,19 +16468,19 @@
         <v>367</v>
       </c>
       <c r="F62">
+        <v>4.2</v>
+      </c>
+      <c r="G62">
+        <v>4.6</v>
+      </c>
+      <c r="H62">
+        <v>1.89</v>
+      </c>
+      <c r="I62">
+        <v>1.92</v>
+      </c>
+      <c r="J62">
         <v>3.95</v>
-      </c>
-      <c r="G62">
-        <v>4.5</v>
-      </c>
-      <c r="H62">
-        <v>1.91</v>
-      </c>
-      <c r="I62">
-        <v>2</v>
-      </c>
-      <c r="J62">
-        <v>3.9</v>
       </c>
       <c r="K62">
         <v>4.3</v>
@@ -16498,10 +16498,10 @@
         <v>0</v>
       </c>
       <c r="P62">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q62">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R62">
         <v>0</v>
@@ -16952,7 +16952,7 @@
         <v>369</v>
       </c>
       <c r="F64">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G64">
         <v>2.34</v>
@@ -16961,7 +16961,7 @@
         <v>3.25</v>
       </c>
       <c r="I64">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J64">
         <v>3.7</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="P64">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="Q64">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -17194,13 +17194,13 @@
         <v>370</v>
       </c>
       <c r="F65">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G65">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H65">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I65">
         <v>2.28</v>
@@ -17227,7 +17227,7 @@
         <v>2.06</v>
       </c>
       <c r="Q65">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R65">
         <v>0</v>
@@ -17436,13 +17436,13 @@
         <v>371</v>
       </c>
       <c r="F66">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="G66">
         <v>3.2</v>
       </c>
       <c r="H66">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="I66">
         <v>2.8</v>
@@ -17451,7 +17451,7 @@
         <v>3.6</v>
       </c>
       <c r="K66">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -17684,13 +17684,13 @@
         <v>2.98</v>
       </c>
       <c r="H67">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I67">
         <v>2.84</v>
       </c>
       <c r="J67">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K67">
         <v>3.65</v>
@@ -17708,7 +17708,7 @@
         <v>0</v>
       </c>
       <c r="P67">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q67">
         <v>1.79</v>
@@ -17920,7 +17920,7 @@
         <v>373</v>
       </c>
       <c r="F68">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G68">
         <v>1.52</v>
@@ -18192,10 +18192,10 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="Q69">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         <v>3.35</v>
       </c>
       <c r="G72">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H72">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I72">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J72">
         <v>3.6</v>
@@ -18915,19 +18915,19 @@
         <v>4.3</v>
       </c>
       <c r="O72">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P72">
         <v>2.12</v>
       </c>
       <c r="Q72">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R72">
         <v>1.44</v>
       </c>
       <c r="S72">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T72">
         <v>1.7</v>
@@ -18942,7 +18942,7 @@
         <v>0</v>
       </c>
       <c r="X72">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y72">
         <v>11.5</v>
@@ -18960,7 +18960,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD72">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE72">
         <v>23</v>
@@ -18969,7 +18969,7 @@
         <v>25</v>
       </c>
       <c r="AG72">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH72">
         <v>16</v>
@@ -18987,7 +18987,7 @@
         <v>46</v>
       </c>
       <c r="AM72">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN72">
         <v>32</v>
@@ -18996,7 +18996,7 @@
         <v>15.5</v>
       </c>
       <c r="AP72">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ72">
         <v>10.5</v>
@@ -19008,7 +19008,7 @@
         <v>19.5</v>
       </c>
       <c r="AT72">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU72">
         <v>7.8</v>
@@ -19017,7 +19017,7 @@
         <v>10</v>
       </c>
       <c r="AW72">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX72">
         <v>21</v>
@@ -19038,7 +19038,7 @@
         <v>30</v>
       </c>
       <c r="BD72">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BE72">
         <v>34</v>
@@ -19047,7 +19047,7 @@
         <v>19</v>
       </c>
       <c r="BG72">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH72">
         <v>1000</v>
@@ -19130,22 +19130,22 @@
         <v>378</v>
       </c>
       <c r="F73">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="G73">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="H73">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="I73">
-        <v>28</v>
+        <v>9.6</v>
       </c>
       <c r="J73">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K73">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -19160,10 +19160,10 @@
         <v>0</v>
       </c>
       <c r="P73">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="Q73">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -19375,7 +19375,7 @@
         <v>2.04</v>
       </c>
       <c r="G74">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H74">
         <v>3.15</v>
@@ -19402,7 +19402,7 @@
         <v>0</v>
       </c>
       <c r="P74">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q74">
         <v>1.55</v>
@@ -19614,7 +19614,7 @@
         <v>380</v>
       </c>
       <c r="F75">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G75">
         <v>1.67</v>
@@ -19644,7 +19644,7 @@
         <v>0</v>
       </c>
       <c r="P75">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q75">
         <v>1.4</v>
@@ -19856,7 +19856,7 @@
         <v>381</v>
       </c>
       <c r="F76">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G76">
         <v>2.5</v>
@@ -19871,7 +19871,7 @@
         <v>3.7</v>
       </c>
       <c r="K76">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -19886,10 +19886,10 @@
         <v>0</v>
       </c>
       <c r="P76">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q76">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -20098,22 +20098,22 @@
         <v>382</v>
       </c>
       <c r="F77">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G77">
         <v>2.96</v>
       </c>
       <c r="H77">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I77">
         <v>3.1</v>
       </c>
       <c r="J77">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K77">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -20131,7 +20131,7 @@
         <v>1.83</v>
       </c>
       <c r="Q77">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -20340,22 +20340,22 @@
         <v>383</v>
       </c>
       <c r="F78">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G78">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H78">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I78">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J78">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K78">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -20370,10 +20370,10 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q78">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -20588,7 +20588,7 @@
         <v>2.5</v>
       </c>
       <c r="H79">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I79">
         <v>3.45</v>
@@ -20597,7 +20597,7 @@
         <v>3.55</v>
       </c>
       <c r="K79">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -20824,16 +20824,16 @@
         <v>385</v>
       </c>
       <c r="F80">
-        <v>1.72</v>
+        <v>2.92</v>
       </c>
       <c r="G80">
         <v>3.5</v>
       </c>
       <c r="H80">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I80">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J80">
         <v>3.9</v>
@@ -20857,7 +20857,7 @@
         <v>2.92</v>
       </c>
       <c r="Q80">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -21066,13 +21066,13 @@
         <v>386</v>
       </c>
       <c r="F81">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G81">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H81">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I81">
         <v>5</v>
@@ -21081,7 +21081,7 @@
         <v>3.45</v>
       </c>
       <c r="K81">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -21096,10 +21096,10 @@
         <v>0</v>
       </c>
       <c r="P81">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q81">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -21308,19 +21308,19 @@
         <v>387</v>
       </c>
       <c r="F82">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G82">
         <v>3.3</v>
       </c>
       <c r="H82">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I82">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J82">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K82">
         <v>3.7</v>
@@ -21362,7 +21362,7 @@
         <v>0</v>
       </c>
       <c r="X82">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y82">
         <v>12</v>
@@ -21383,19 +21383,19 @@
         <v>11.5</v>
       </c>
       <c r="AE82">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF82">
         <v>24</v>
       </c>
       <c r="AG82">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH82">
         <v>16</v>
       </c>
       <c r="AI82">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ82">
         <v>60</v>
@@ -21404,13 +21404,13 @@
         <v>34</v>
       </c>
       <c r="AL82">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM82">
         <v>85</v>
       </c>
       <c r="AN82">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO82">
         <v>16.5</v>
@@ -21455,16 +21455,16 @@
         <v>40</v>
       </c>
       <c r="BC82">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD82">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE82">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BF82">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG82">
         <v>14</v>
@@ -21550,22 +21550,22 @@
         <v>388</v>
       </c>
       <c r="F83">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G83">
         <v>2.24</v>
       </c>
       <c r="H83">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I83">
         <v>4.2</v>
       </c>
       <c r="J83">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K83">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -21580,7 +21580,7 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q83">
         <v>1.31</v>
@@ -21792,22 +21792,22 @@
         <v>389</v>
       </c>
       <c r="F84">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="G84">
         <v>3.5</v>
       </c>
       <c r="H84">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="I84">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="J84">
         <v>3.3</v>
       </c>
       <c r="K84">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -21822,10 +21822,10 @@
         <v>0</v>
       </c>
       <c r="P84">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="Q84">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -22040,13 +22040,13 @@
         <v>7.6</v>
       </c>
       <c r="H85">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I85">
         <v>1.55</v>
       </c>
       <c r="J85">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K85">
         <v>5.4</v>
@@ -22521,19 +22521,19 @@
         <v>3.7</v>
       </c>
       <c r="G87">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H87">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="I87">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J87">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K87">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L87">
         <v>1.01</v>
@@ -22542,22 +22542,22 @@
         <v>1.01</v>
       </c>
       <c r="N87">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O87">
         <v>1.31</v>
       </c>
       <c r="P87">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q87">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R87">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S87">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T87">
         <v>1.01</v>
@@ -22566,7 +22566,7 @@
         <v>1.01</v>
       </c>
       <c r="V87">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W87">
         <v>1.2</v>
@@ -23005,16 +23005,16 @@
         <v>2.82</v>
       </c>
       <c r="G89">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="H89">
         <v>2.66</v>
       </c>
       <c r="I89">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="J89">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="K89">
         <v>3.5</v>
@@ -23032,10 +23032,10 @@
         <v>0</v>
       </c>
       <c r="P89">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q89">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -23250,16 +23250,16 @@
         <v>2.42</v>
       </c>
       <c r="H90">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I90">
         <v>3.6</v>
       </c>
       <c r="J90">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K90">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q90">
         <v>1.42</v>
@@ -23728,22 +23728,22 @@
         <v>397</v>
       </c>
       <c r="F92">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G92">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H92">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="I92">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J92">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K92">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -23758,10 +23758,10 @@
         <v>0</v>
       </c>
       <c r="P92">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="Q92">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -23973,10 +23973,10 @@
         <v>4.6</v>
       </c>
       <c r="G93">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H93">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I93">
         <v>1.8</v>
@@ -24000,7 +24000,7 @@
         <v>0</v>
       </c>
       <c r="P93">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q93">
         <v>1.63</v>
@@ -24454,22 +24454,22 @@
         <v>400</v>
       </c>
       <c r="F95">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="G95">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H95">
         <v>7</v>
       </c>
       <c r="I95">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="J95">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K95">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -24484,7 +24484,7 @@
         <v>0</v>
       </c>
       <c r="P95">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q95">
         <v>1.39</v>
@@ -24696,13 +24696,13 @@
         <v>401</v>
       </c>
       <c r="F96">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G96">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="H96">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="I96">
         <v>8.6</v>
@@ -24711,7 +24711,7 @@
         <v>3.9</v>
       </c>
       <c r="K96">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -24816,7 +24816,7 @@
         <v>5.9</v>
       </c>
       <c r="AT96">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="AU96">
         <v>3.85</v>
@@ -24831,7 +24831,7 @@
         <v>4.1</v>
       </c>
       <c r="AY96">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ96">
         <v>4.7</v>
@@ -24843,7 +24843,7 @@
         <v>4.4</v>
       </c>
       <c r="BC96">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="BD96">
         <v>5.3</v>
@@ -24941,7 +24941,7 @@
         <v>2.22</v>
       </c>
       <c r="G97">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H97">
         <v>3.1</v>
@@ -25183,10 +25183,10 @@
         <v>1.48</v>
       </c>
       <c r="G98">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H98">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="I98">
         <v>11</v>
@@ -25195,7 +25195,7 @@
         <v>4.3</v>
       </c>
       <c r="K98">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -25210,10 +25210,10 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q98">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -25664,19 +25664,19 @@
         <v>405</v>
       </c>
       <c r="F100">
-        <v>1.74</v>
+        <v>1.32</v>
       </c>
       <c r="G100">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="H100">
-        <v>4.1</v>
+        <v>1.32</v>
       </c>
       <c r="I100">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="J100">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K100">
         <v>4.1</v>
@@ -25694,7 +25694,7 @@
         <v>0</v>
       </c>
       <c r="P100">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q100">
         <v>1.86</v>
@@ -25909,19 +25909,19 @@
         <v>3.35</v>
       </c>
       <c r="G101">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="H101">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="I101">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J101">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K101">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -25936,10 +25936,10 @@
         <v>0</v>
       </c>
       <c r="P101">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q101">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -26157,7 +26157,7 @@
         <v>4</v>
       </c>
       <c r="I102">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J102">
         <v>3.3</v>
@@ -26193,7 +26193,7 @@
         <v>2.04</v>
       </c>
       <c r="U102">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V102">
         <v>0</v>
@@ -26208,13 +26208,13 @@
         <v>12.5</v>
       </c>
       <c r="Z102">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA102">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB102">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC102">
         <v>7.4</v>
@@ -26223,7 +26223,7 @@
         <v>17</v>
       </c>
       <c r="AE102">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF102">
         <v>12.5</v>
@@ -26235,10 +26235,10 @@
         <v>21</v>
       </c>
       <c r="AI102">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ102">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK102">
         <v>29</v>
@@ -26253,10 +26253,10 @@
         <v>23</v>
       </c>
       <c r="AO102">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP102">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ102">
         <v>11</v>
@@ -26277,7 +26277,7 @@
         <v>15.5</v>
       </c>
       <c r="AW102">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AX102">
         <v>11</v>
@@ -26289,10 +26289,10 @@
         <v>19</v>
       </c>
       <c r="BA102">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB102">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC102">
         <v>17.5</v>
@@ -26310,64 +26310,64 @@
         <v>34</v>
       </c>
       <c r="BH102">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI102">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ102">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK102">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL102">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM102">
         <v>1.01</v>
       </c>
       <c r="BN102">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO102">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP102">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ102">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BR102">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS102">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT102">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU102">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV102">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW102">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BX102">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY102">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ102">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA102">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="CB102" t="s">
         <v>446</v>
@@ -26390,19 +26390,19 @@
         <v>408</v>
       </c>
       <c r="F103">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G103">
         <v>2.64</v>
       </c>
       <c r="H103">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I103">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J103">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="K103">
         <v>3.35</v>
@@ -26420,10 +26420,10 @@
         <v>0</v>
       </c>
       <c r="P103">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="Q103">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -26632,7 +26632,7 @@
         <v>409</v>
       </c>
       <c r="F104">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G104">
         <v>4.2</v>
@@ -26641,13 +26641,13 @@
         <v>2.16</v>
       </c>
       <c r="I104">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J104">
         <v>3.4</v>
       </c>
       <c r="K104">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -26665,7 +26665,7 @@
         <v>1.73</v>
       </c>
       <c r="Q104">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -27361,7 +27361,7 @@
         <v>1.78</v>
       </c>
       <c r="G107">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H107">
         <v>4.8</v>
@@ -27388,10 +27388,10 @@
         <v>0</v>
       </c>
       <c r="P107">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q107">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -27842,19 +27842,19 @@
         <v>414</v>
       </c>
       <c r="F109">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G109">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H109">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="I109">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J109">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K109">
         <v>3.5</v>
@@ -27872,10 +27872,10 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q109">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -28084,22 +28084,22 @@
         <v>415</v>
       </c>
       <c r="F110">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="G110">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="H110">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="I110">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="J110">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K110">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -28114,7 +28114,7 @@
         <v>0</v>
       </c>
       <c r="P110">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q110">
         <v>1.84</v>
@@ -28338,7 +28338,7 @@
         <v>4.6</v>
       </c>
       <c r="J111">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K111">
         <v>4.1</v>
@@ -28356,10 +28356,10 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q111">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -28568,22 +28568,22 @@
         <v>417</v>
       </c>
       <c r="F112">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="G112">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H112">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="I112">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J112">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="K112">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L112">
         <v>0</v>
@@ -28601,7 +28601,7 @@
         <v>1.25</v>
       </c>
       <c r="Q112">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -28810,7 +28810,7 @@
         <v>418</v>
       </c>
       <c r="F113">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="G113">
         <v>5.7</v>
@@ -28819,10 +28819,10 @@
         <v>1.79</v>
       </c>
       <c r="I113">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="J113">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K113">
         <v>4.2</v>
@@ -28840,7 +28840,7 @@
         <v>0</v>
       </c>
       <c r="P113">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q113">
         <v>1.67</v>
@@ -29536,10 +29536,10 @@
         <v>421</v>
       </c>
       <c r="F116">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G116">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H116">
         <v>4.2</v>
@@ -29551,7 +29551,7 @@
         <v>3.4</v>
       </c>
       <c r="K116">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L116">
         <v>0</v>
@@ -29566,7 +29566,7 @@
         <v>0</v>
       </c>
       <c r="P116">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q116">
         <v>1.64</v>
@@ -29778,22 +29778,22 @@
         <v>422</v>
       </c>
       <c r="F117">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G117">
         <v>3.5</v>
       </c>
       <c r="H117">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="I117">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J117">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="K117">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L117">
         <v>0</v>
@@ -29808,10 +29808,10 @@
         <v>0</v>
       </c>
       <c r="P117">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q117">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -30504,22 +30504,22 @@
         <v>425</v>
       </c>
       <c r="F120">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="G120">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="H120">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="I120">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="J120">
         <v>3.55</v>
       </c>
       <c r="K120">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="L120">
         <v>0</v>
@@ -30534,7 +30534,7 @@
         <v>0</v>
       </c>
       <c r="P120">
-        <v>1.07</v>
+        <v>1.66</v>
       </c>
       <c r="Q120">
         <v>2.14</v>
@@ -31230,19 +31230,19 @@
         <v>428</v>
       </c>
       <c r="F123">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G123">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H123">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I123">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J123">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K123">
         <v>3.7</v>
@@ -31263,7 +31263,7 @@
         <v>2</v>
       </c>
       <c r="Q123">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -31478,7 +31478,7 @@
         <v>3.1</v>
       </c>
       <c r="H124">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I124">
         <v>3.3</v>
@@ -31496,19 +31496,19 @@
         <v>1.01</v>
       </c>
       <c r="N124">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O124">
         <v>1.34</v>
       </c>
       <c r="P124">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q124">
         <v>1.84</v>
       </c>
       <c r="R124">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S124">
         <v>3.3</v>
@@ -31520,7 +31520,7 @@
         <v>1.01</v>
       </c>
       <c r="V124">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W124">
         <v>1.47</v>
@@ -31720,7 +31720,7 @@
         <v>1.36</v>
       </c>
       <c r="H125">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I125">
         <v>11</v>
@@ -31744,7 +31744,7 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="Q125">
         <v>1.51</v>
@@ -32198,7 +32198,7 @@
         <v>432</v>
       </c>
       <c r="F127">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="G127">
         <v>1.94</v>
@@ -32207,7 +32207,7 @@
         <v>4.7</v>
       </c>
       <c r="I127">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J127">
         <v>3.55</v>
@@ -32440,22 +32440,22 @@
         <v>433</v>
       </c>
       <c r="F128">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="G128">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H128">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I128">
         <v>5.4</v>
       </c>
       <c r="J128">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K128">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L128">
         <v>0</v>
@@ -32470,10 +32470,10 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q128">
-        <v>2</v>
+        <v>1.02</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -32682,22 +32682,22 @@
         <v>434</v>
       </c>
       <c r="F129">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="G129">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H129">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I129">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J129">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K129">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L129">
         <v>0</v>
@@ -32712,10 +32712,10 @@
         <v>0</v>
       </c>
       <c r="P129">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q129">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -32924,13 +32924,13 @@
         <v>435</v>
       </c>
       <c r="F130">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G130">
         <v>5.1</v>
       </c>
       <c r="H130">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I130">
         <v>1.93</v>
@@ -32954,10 +32954,10 @@
         <v>0</v>
       </c>
       <c r="P130">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="Q130">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -33166,13 +33166,13 @@
         <v>436</v>
       </c>
       <c r="F131">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G131">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H131">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I131">
         <v>5.5</v>
@@ -33181,7 +33181,7 @@
         <v>3.25</v>
       </c>
       <c r="K131">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L131">
         <v>0</v>
@@ -33199,7 +33199,7 @@
         <v>1.6</v>
       </c>
       <c r="Q131">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -33656,16 +33656,16 @@
         <v>1.85</v>
       </c>
       <c r="H133">
-        <v>4.5</v>
+        <v>2.16</v>
       </c>
       <c r="I133">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J133">
-        <v>3.75</v>
+        <v>2.16</v>
       </c>
       <c r="K133">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -33904,7 +33904,7 @@
         <v>3.1</v>
       </c>
       <c r="J134">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="K134">
         <v>7.6</v>
@@ -34134,16 +34134,16 @@
         <v>440</v>
       </c>
       <c r="F135">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G135">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H135">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I135">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J135">
         <v>3.75</v>
@@ -34164,7 +34164,7 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q135">
         <v>2.02</v>
@@ -34376,22 +34376,22 @@
         <v>441</v>
       </c>
       <c r="F136">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G136">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H136">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I136">
         <v>5.7</v>
       </c>
       <c r="J136">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K136">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L136">
         <v>0</v>
@@ -34624,7 +34624,7 @@
         <v>1.79</v>
       </c>
       <c r="H137">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I137">
         <v>1000</v>
@@ -34648,7 +34648,7 @@
         <v>0</v>
       </c>
       <c r="P137">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="Q137">
         <v>1.94</v>
@@ -35344,7 +35344,7 @@
         <v>445</v>
       </c>
       <c r="F140">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G140">
         <v>6.4</v>
@@ -35356,10 +35356,10 @@
         <v>1.91</v>
       </c>
       <c r="J140">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K140">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L140">
         <v>0</v>
@@ -35377,7 +35377,7 @@
         <v>1.74</v>
       </c>
       <c r="Q140">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -35386,10 +35386,10 @@
         <v>0</v>
       </c>
       <c r="T140">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U140">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V140">
         <v>0</v>
@@ -35434,10 +35434,10 @@
         <v>48</v>
       </c>
       <c r="AJ140">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK140">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AL140">
         <v>95</v>
@@ -35446,46 +35446,46 @@
         <v>160</v>
       </c>
       <c r="AN140">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AO140">
         <v>16.5</v>
       </c>
       <c r="AP140">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AQ140">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="AR140">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="AS140">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="AT140">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="AU140">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="AV140">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="AW140">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="AX140">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AY140">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="AZ140">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BA140">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB140">
         <v>5</v>
@@ -35503,7 +35503,7 @@
         <v>5</v>
       </c>
       <c r="BG140">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="BH140">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-16.xlsx
@@ -1354,7 +1354,7 @@
     <t>Universitario de Deportes</t>
   </si>
   <si>
-    <t>2026-08-14 05:18:48</t>
+    <t>2026-08-14 07:43:50</t>
   </si>
 </sst>
 </file>
@@ -1954,7 +1954,7 @@
         <v>1.8</v>
       </c>
       <c r="H2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I2">
         <v>5.8</v>
@@ -1963,7 +1963,7 @@
         <v>3.75</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1978,7 +1978,7 @@
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Q2">
         <v>1.98</v>
@@ -1987,7 +1987,7 @@
         <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T2">
         <v>1.89</v>
@@ -1996,13 +1996,13 @@
         <v>1.94</v>
       </c>
       <c r="V2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
         <v>2.24</v>
       </c>
       <c r="X2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
         <v>18.5</v>
@@ -2014,7 +2014,7 @@
         <v>160</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
         <v>8.800000000000001</v>
@@ -2026,7 +2026,7 @@
         <v>90</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -2065,7 +2065,7 @@
         <v>29</v>
       </c>
       <c r="AS2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
@@ -2077,7 +2077,7 @@
         <v>16</v>
       </c>
       <c r="AW2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX2">
         <v>9.199999999999999</v>
@@ -2086,10 +2086,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>5.3</v>
       </c>
       <c r="BA2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB2">
         <v>14.5</v>
@@ -2101,13 +2101,13 @@
         <v>28</v>
       </c>
       <c r="BE2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF2">
         <v>10.5</v>
       </c>
       <c r="BG2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -2214,7 +2214,7 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O3">
         <v>1.31</v>
@@ -2223,7 +2223,7 @@
         <v>1.78</v>
       </c>
       <c r="Q3">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R3">
         <v>1.28</v>
@@ -2435,13 +2435,13 @@
         <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H4">
         <v>3.5</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -2480,10 +2480,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -2677,13 +2677,13 @@
         <v>4.1</v>
       </c>
       <c r="G5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H5">
         <v>2.22</v>
       </c>
       <c r="I5">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -2695,22 +2695,22 @@
         <v>1.62</v>
       </c>
       <c r="M5">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N5">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P5">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q5">
         <v>3</v>
       </c>
       <c r="R5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S5">
         <v>6.6</v>
@@ -2722,13 +2722,13 @@
         <v>1.63</v>
       </c>
       <c r="V5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W5">
         <v>1.28</v>
       </c>
       <c r="X5">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>6.6</v>
@@ -2758,10 +2758,10 @@
         <v>23</v>
       </c>
       <c r="AH5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
         <v>120</v>
@@ -2770,13 +2770,13 @@
         <v>90</v>
       </c>
       <c r="AL5">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM5">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO5">
         <v>42</v>
@@ -2824,13 +2824,13 @@
         <v>70</v>
       </c>
       <c r="BD5">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BG5">
         <v>28</v>
@@ -2922,7 +2922,7 @@
         <v>1.26</v>
       </c>
       <c r="H6">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="I6">
         <v>25</v>
@@ -2931,7 +2931,7 @@
         <v>6.4</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L6">
         <v>1.21</v>
@@ -2949,10 +2949,10 @@
         <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="R6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S6">
         <v>2.7</v>
@@ -2967,10 +2967,10 @@
         <v>1.04</v>
       </c>
       <c r="W6">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="X6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y6">
         <v>65</v>
@@ -2985,7 +2985,7 @@
         <v>8.4</v>
       </c>
       <c r="AC6">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AD6">
         <v>95</v>
@@ -2994,10 +2994,10 @@
         <v>1000</v>
       </c>
       <c r="AF6">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH6">
         <v>60</v>
@@ -3012,10 +3012,10 @@
         <v>18.5</v>
       </c>
       <c r="AL6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM6">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="AN6">
         <v>4.8</v>
@@ -3024,58 +3024,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="AQ6">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AR6">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AS6">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AT6">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="AU6">
         <v>13.5</v>
       </c>
       <c r="AV6">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AW6">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AX6">
-        <v>3.55</v>
+        <v>5.9</v>
       </c>
       <c r="AY6">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA6">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BB6">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC6">
         <v>11</v>
       </c>
       <c r="BD6">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BE6">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BF6">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="BG6">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -3099,13 +3099,13 @@
         <v>4.6</v>
       </c>
       <c r="BO6">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BP6">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BR6">
         <v>44</v>
@@ -3158,16 +3158,16 @@
         <v>312</v>
       </c>
       <c r="F7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G7">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
       <c r="I7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3185,25 +3185,25 @@
         <v>6.6</v>
       </c>
       <c r="O7">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P7">
         <v>2.9</v>
       </c>
       <c r="Q7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R7">
         <v>1.78</v>
       </c>
       <c r="S7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T7">
         <v>1.47</v>
       </c>
       <c r="U7">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="V7">
         <v>1.46</v>
@@ -3218,7 +3218,7 @@
         <v>22</v>
       </c>
       <c r="Z7">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AA7">
         <v>220</v>
@@ -3227,7 +3227,7 @@
         <v>18.5</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD7">
         <v>14.5</v>
@@ -3248,10 +3248,10 @@
         <v>32</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK7">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AL7">
         <v>27</v>
@@ -3266,7 +3266,7 @@
         <v>16.5</v>
       </c>
       <c r="AP7">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AQ7">
         <v>17.5</v>
@@ -3278,13 +3278,13 @@
         <v>32</v>
       </c>
       <c r="AT7">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AU7">
         <v>9.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW7">
         <v>18.5</v>
@@ -3314,10 +3314,10 @@
         <v>29</v>
       </c>
       <c r="BF7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3332,7 +3332,7 @@
         <v>5.4</v>
       </c>
       <c r="BL7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BM7">
         <v>21</v>
@@ -3400,22 +3400,22 @@
         <v>313</v>
       </c>
       <c r="F8">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G8">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J8">
         <v>4.1</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
         <v>1.31</v>
@@ -3448,10 +3448,10 @@
         <v>2.36</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X8">
         <v>24</v>
@@ -3460,7 +3460,7 @@
         <v>23</v>
       </c>
       <c r="Z8">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -3490,31 +3490,31 @@
         <v>55</v>
       </c>
       <c r="AJ8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK8">
         <v>17.5</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM8">
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO8">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AP8">
         <v>16.5</v>
       </c>
       <c r="AQ8">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AR8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS8">
         <v>38</v>
@@ -3526,22 +3526,22 @@
         <v>9</v>
       </c>
       <c r="AV8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AW8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX8">
         <v>11</v>
       </c>
       <c r="AY8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8">
         <v>15</v>
       </c>
       <c r="BA8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB8">
         <v>16.5</v>
@@ -3550,16 +3550,16 @@
         <v>14.5</v>
       </c>
       <c r="BD8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE8">
         <v>32</v>
       </c>
       <c r="BF8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3666,7 +3666,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O9">
         <v>1.18</v>
@@ -3678,10 +3678,10 @@
         <v>1.45</v>
       </c>
       <c r="R9">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="S9">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -3899,7 +3899,7 @@
         <v>2.38</v>
       </c>
       <c r="K10">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -4129,19 +4129,19 @@
         <v>1.51</v>
       </c>
       <c r="G11">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I11">
         <v>7.2</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L11">
         <v>1.26</v>
@@ -4153,7 +4153,7 @@
         <v>6.4</v>
       </c>
       <c r="O11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P11">
         <v>2.84</v>
@@ -4168,16 +4168,16 @@
         <v>2.28</v>
       </c>
       <c r="T11">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U11">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
         <v>1.17</v>
       </c>
       <c r="W11">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="X11">
         <v>34</v>
@@ -4198,13 +4198,13 @@
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE11">
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG11">
         <v>10.5</v>
@@ -4213,7 +4213,7 @@
         <v>20</v>
       </c>
       <c r="AI11">
-        <v>920</v>
+        <v>860</v>
       </c>
       <c r="AJ11">
         <v>15.5</v>
@@ -4231,10 +4231,10 @@
         <v>5.3</v>
       </c>
       <c r="AO11">
-        <v>940</v>
+        <v>880</v>
       </c>
       <c r="AP11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AQ11">
         <v>25</v>
@@ -4264,7 +4264,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA11">
         <v>30</v>
@@ -4383,7 +4383,7 @@
         <v>4</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>1.3</v>
@@ -4410,7 +4410,7 @@
         <v>2.6</v>
       </c>
       <c r="T12">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="U12">
         <v>2.42</v>
@@ -4455,7 +4455,7 @@
         <v>20</v>
       </c>
       <c r="AI12">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AJ12">
         <v>28</v>
@@ -4476,22 +4476,22 @@
         <v>100</v>
       </c>
       <c r="AP12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ12">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AR12">
         <v>26</v>
       </c>
       <c r="AS12">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT12">
         <v>10</v>
       </c>
       <c r="AU12">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
         <v>14</v>
@@ -4500,16 +4500,16 @@
         <v>34</v>
       </c>
       <c r="AX12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
         <v>12.5</v>
       </c>
       <c r="BA12">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BB12">
         <v>15</v>
@@ -4518,7 +4518,7 @@
         <v>12.5</v>
       </c>
       <c r="BD12">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE12">
         <v>42</v>
@@ -4640,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q13">
         <v>1.89</v>
@@ -4852,10 +4852,10 @@
         <v>319</v>
       </c>
       <c r="F14">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G14">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H14">
         <v>5.1</v>
@@ -4867,7 +4867,7 @@
         <v>4.6</v>
       </c>
       <c r="K14">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>1.26</v>
@@ -4876,7 +4876,7 @@
         <v>1.03</v>
       </c>
       <c r="N14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O14">
         <v>1.17</v>
@@ -4897,13 +4897,13 @@
         <v>1.59</v>
       </c>
       <c r="U14">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V14">
         <v>1.22</v>
       </c>
       <c r="W14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X14">
         <v>34</v>
@@ -4972,7 +4972,7 @@
         <v>40</v>
       </c>
       <c r="AT14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU14">
         <v>10.5</v>
@@ -5094,19 +5094,19 @@
         <v>320</v>
       </c>
       <c r="F15">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G15">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H15">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I15">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -5118,13 +5118,13 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q15">
         <v>1.54</v>
@@ -5133,46 +5133,46 @@
         <v>1.7</v>
       </c>
       <c r="S15">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T15">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U15">
         <v>2.76</v>
       </c>
       <c r="V15">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X15">
         <v>48</v>
       </c>
       <c r="Y15">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Z15">
         <v>32</v>
       </c>
       <c r="AA15">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="AB15">
         <v>16</v>
       </c>
       <c r="AC15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD15">
         <v>15.5</v>
       </c>
       <c r="AE15">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF15">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
@@ -5181,10 +5181,10 @@
         <v>15.5</v>
       </c>
       <c r="AI15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ15">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK15">
         <v>20</v>
@@ -5193,10 +5193,10 @@
         <v>27</v>
       </c>
       <c r="AM15">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN15">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO15">
         <v>21</v>
@@ -5208,22 +5208,22 @@
         <v>17.5</v>
       </c>
       <c r="AR15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT15">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU15">
         <v>9.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW15">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX15">
         <v>15</v>
@@ -5232,13 +5232,13 @@
         <v>10</v>
       </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC15">
         <v>16</v>
@@ -5247,13 +5247,13 @@
         <v>21</v>
       </c>
       <c r="BE15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BF15">
         <v>8.6</v>
       </c>
       <c r="BG15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -5262,58 +5262,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB15" t="s">
         <v>446</v>
@@ -5345,7 +5345,7 @@
         <v>2.24</v>
       </c>
       <c r="I16">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="J16">
         <v>2.84</v>
@@ -5372,10 +5372,10 @@
         <v>2.1</v>
       </c>
       <c r="R16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="S16">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -5587,7 +5587,7 @@
         <v>2.84</v>
       </c>
       <c r="I17">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J17">
         <v>3.6</v>
@@ -5596,16 +5596,16 @@
         <v>5.9</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P17">
         <v>2.04</v>
@@ -5614,184 +5614,184 @@
         <v>1.7</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5823,31 +5823,31 @@
         <v>1.99</v>
       </c>
       <c r="G18">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="H18">
         <v>3.35</v>
       </c>
       <c r="I18">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J18">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K18">
         <v>5.1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P18">
         <v>1.62</v>
@@ -5856,184 +5856,184 @@
         <v>1.96</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -6080,208 +6080,208 @@
         <v>320</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
         <v>446</v>
@@ -6322,16 +6322,16 @@
         <v>3.7</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P20">
         <v>1.47</v>
@@ -6340,184 +6340,184 @@
         <v>2.24</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
         <v>0</v>
@@ -6546,226 +6546,226 @@
         <v>326</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P21">
+        <v>1.67</v>
+      </c>
+      <c r="Q21">
+        <v>1.9</v>
+      </c>
+      <c r="R21">
         <v>1.24</v>
       </c>
-      <c r="Q21">
-        <v>1.01</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
       <c r="S21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
         <v>446</v>
@@ -6791,31 +6791,31 @@
         <v>2.84</v>
       </c>
       <c r="G22">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H22">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I22">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J22">
         <v>3.6</v>
       </c>
       <c r="K22">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
         <v>2.26</v>
@@ -6824,190 +6824,190 @@
         <v>1.64</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
         <v>446</v>
@@ -7030,226 +7030,226 @@
         <v>328</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P23">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
         <v>446</v>
@@ -7272,226 +7272,226 @@
         <v>329</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P24">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
         <v>446</v>
@@ -7514,226 +7514,226 @@
         <v>330</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P25">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
         <v>446</v>
@@ -7756,220 +7756,220 @@
         <v>331</v>
       </c>
       <c r="F26">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="G26">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="H26">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="I26">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="J26">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="K26">
-        <v>320</v>
+        <v>14.5</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P26">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q26">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -8010,10 +8010,10 @@
         <v>1000</v>
       </c>
       <c r="J27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K27">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -8482,19 +8482,19 @@
         <v>334</v>
       </c>
       <c r="F29">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="G29">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H29">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I29">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="J29">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K29">
         <v>3.9</v>
@@ -8515,7 +8515,7 @@
         <v>2.06</v>
       </c>
       <c r="Q29">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8736,10 +8736,10 @@
         <v>1000</v>
       </c>
       <c r="J30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K30">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8996,10 +8996,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.92</v>
+        <v>2.54</v>
       </c>
       <c r="Q31">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -9453,16 +9453,16 @@
         <v>2.18</v>
       </c>
       <c r="G33">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H33">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I33">
         <v>3.55</v>
       </c>
       <c r="J33">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K33">
         <v>4.1</v>
@@ -9692,22 +9692,22 @@
         <v>339</v>
       </c>
       <c r="F34">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="G34">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H34">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I34">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J34">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K34">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9722,10 +9722,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q34">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>340</v>
       </c>
       <c r="F35">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G35">
         <v>1.63</v>
@@ -9967,7 +9967,7 @@
         <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -10191,7 +10191,7 @@
         <v>4.1</v>
       </c>
       <c r="K36">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -10666,7 +10666,7 @@
         <v>1.44</v>
       </c>
       <c r="H38">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I38">
         <v>7.8</v>
@@ -10675,7 +10675,7 @@
         <v>5.6</v>
       </c>
       <c r="K38">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -11144,13 +11144,13 @@
         <v>345</v>
       </c>
       <c r="F40">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G40">
         <v>1.79</v>
       </c>
       <c r="H40">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I40">
         <v>5.5</v>
@@ -11159,7 +11159,7 @@
         <v>3.95</v>
       </c>
       <c r="K40">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -11174,10 +11174,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q40">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -11416,7 +11416,7 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q41">
         <v>1.01</v>
@@ -11634,16 +11634,16 @@
         <v>1.45</v>
       </c>
       <c r="H42">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I42">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J42">
         <v>5.5</v>
       </c>
       <c r="K42">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -11658,7 +11658,7 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q42">
         <v>1.37</v>
@@ -11873,16 +11873,16 @@
         <v>3.55</v>
       </c>
       <c r="G43">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H43">
         <v>2.14</v>
       </c>
       <c r="I43">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J43">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K43">
         <v>3.8</v>
@@ -11897,7 +11897,7 @@
         <v>4.4</v>
       </c>
       <c r="O43">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P43">
         <v>2.14</v>
@@ -11915,7 +11915,7 @@
         <v>1.66</v>
       </c>
       <c r="U43">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -11948,7 +11948,7 @@
         <v>22</v>
       </c>
       <c r="AF43">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG43">
         <v>15.5</v>
@@ -12112,22 +12112,22 @@
         <v>349</v>
       </c>
       <c r="F44">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="G44">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H44">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="I44">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="J44">
         <v>4.2</v>
       </c>
       <c r="K44">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -12838,13 +12838,13 @@
         <v>352</v>
       </c>
       <c r="F47">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G47">
         <v>2.92</v>
       </c>
       <c r="H47">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I47">
         <v>2.76</v>
@@ -12853,7 +12853,7 @@
         <v>3.7</v>
       </c>
       <c r="K47">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -14532,7 +14532,7 @@
         <v>359</v>
       </c>
       <c r="F54">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G54">
         <v>2.88</v>
@@ -14541,7 +14541,7 @@
         <v>2.72</v>
       </c>
       <c r="I54">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="J54">
         <v>3.5</v>
@@ -14774,13 +14774,13 @@
         <v>360</v>
       </c>
       <c r="F55">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G55">
         <v>4.9</v>
       </c>
       <c r="H55">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I55">
         <v>2.34</v>
@@ -14807,7 +14807,7 @@
         <v>1.57</v>
       </c>
       <c r="Q55">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -15016,19 +15016,19 @@
         <v>361</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G56">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H56">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I56">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="J56">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K56">
         <v>4.4</v>
@@ -15264,16 +15264,16 @@
         <v>4.5</v>
       </c>
       <c r="H57">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="I57">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="J57">
         <v>4.4</v>
       </c>
       <c r="K57">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -15291,7 +15291,7 @@
         <v>2.52</v>
       </c>
       <c r="Q57">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -15742,7 +15742,7 @@
         <v>364</v>
       </c>
       <c r="F59">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G59">
         <v>3.95</v>
@@ -15751,13 +15751,13 @@
         <v>2.08</v>
       </c>
       <c r="I59">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="J59">
         <v>3.45</v>
       </c>
       <c r="K59">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="P64">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q64">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -17442,7 +17442,7 @@
         <v>3.2</v>
       </c>
       <c r="H66">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="I66">
         <v>2.8</v>
@@ -17451,7 +17451,7 @@
         <v>3.6</v>
       </c>
       <c r="K66">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -17678,7 +17678,7 @@
         <v>372</v>
       </c>
       <c r="F67">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G67">
         <v>2.98</v>
@@ -17693,7 +17693,7 @@
         <v>3.4</v>
       </c>
       <c r="K67">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -17708,7 +17708,7 @@
         <v>0</v>
       </c>
       <c r="P67">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Q67">
         <v>1.79</v>
@@ -17923,19 +17923,19 @@
         <v>1.49</v>
       </c>
       <c r="G68">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H68">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I68">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J68">
         <v>5.1</v>
       </c>
       <c r="K68">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -17953,7 +17953,7 @@
         <v>2.98</v>
       </c>
       <c r="Q68">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -18192,10 +18192,10 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q69">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -18649,19 +18649,19 @@
         <v>1.96</v>
       </c>
       <c r="G71">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="H71">
         <v>4.2</v>
       </c>
       <c r="I71">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J71">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K71">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -18888,19 +18888,19 @@
         <v>377</v>
       </c>
       <c r="F72">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G72">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H72">
         <v>2.28</v>
       </c>
       <c r="I72">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J72">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K72">
         <v>3.7</v>
@@ -18918,10 +18918,10 @@
         <v>1.28</v>
       </c>
       <c r="P72">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q72">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R72">
         <v>1.44</v>
@@ -18951,10 +18951,10 @@
         <v>15.5</v>
       </c>
       <c r="AA72">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB72">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC72">
         <v>8.199999999999999</v>
@@ -19005,13 +19005,13 @@
         <v>14</v>
       </c>
       <c r="AS72">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AT72">
         <v>13.5</v>
       </c>
       <c r="AU72">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV72">
         <v>10</v>
@@ -19020,7 +19020,7 @@
         <v>20</v>
       </c>
       <c r="AX72">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY72">
         <v>13</v>
@@ -19029,7 +19029,7 @@
         <v>14.5</v>
       </c>
       <c r="BA72">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BB72">
         <v>28</v>
@@ -19044,10 +19044,10 @@
         <v>34</v>
       </c>
       <c r="BF72">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BG72">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH72">
         <v>1000</v>
@@ -19133,19 +19133,19 @@
         <v>1.46</v>
       </c>
       <c r="G73">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H73">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I73">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J73">
         <v>4.4</v>
       </c>
       <c r="K73">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -19163,7 +19163,7 @@
         <v>2.2</v>
       </c>
       <c r="Q73">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -19372,13 +19372,13 @@
         <v>379</v>
       </c>
       <c r="F74">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G74">
         <v>2.3</v>
       </c>
       <c r="H74">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I74">
         <v>3.95</v>
@@ -19405,7 +19405,7 @@
         <v>2.34</v>
       </c>
       <c r="Q74">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -19859,7 +19859,7 @@
         <v>2.26</v>
       </c>
       <c r="G76">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H76">
         <v>2.96</v>
@@ -20588,16 +20588,16 @@
         <v>2.5</v>
       </c>
       <c r="H79">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I79">
         <v>3.45</v>
       </c>
       <c r="J79">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K79">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -20615,7 +20615,7 @@
         <v>2.3</v>
       </c>
       <c r="Q79">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -20824,7 +20824,7 @@
         <v>385</v>
       </c>
       <c r="F80">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G80">
         <v>3.5</v>
@@ -20833,13 +20833,13 @@
         <v>2.14</v>
       </c>
       <c r="I80">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J80">
         <v>3.9</v>
       </c>
       <c r="K80">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -20854,10 +20854,10 @@
         <v>0</v>
       </c>
       <c r="P80">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q80">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -21072,7 +21072,7 @@
         <v>2.26</v>
       </c>
       <c r="H81">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I81">
         <v>5</v>
@@ -21081,7 +21081,7 @@
         <v>3.45</v>
       </c>
       <c r="K81">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -21099,7 +21099,7 @@
         <v>2.36</v>
       </c>
       <c r="Q81">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -21308,28 +21308,28 @@
         <v>387</v>
       </c>
       <c r="F82">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G82">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H82">
+        <v>2.3</v>
+      </c>
+      <c r="I82">
         <v>2.36</v>
       </c>
-      <c r="I82">
-        <v>2.4</v>
-      </c>
       <c r="J82">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K82">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
       <c r="M82">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N82">
         <v>4.3</v>
@@ -21338,7 +21338,7 @@
         <v>1.26</v>
       </c>
       <c r="P82">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q82">
         <v>1.78</v>
@@ -21374,7 +21374,7 @@
         <v>32</v>
       </c>
       <c r="AB82">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC82">
         <v>8.800000000000001</v>
@@ -21401,7 +21401,7 @@
         <v>60</v>
       </c>
       <c r="AK82">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL82">
         <v>44</v>
@@ -21437,7 +21437,7 @@
         <v>10</v>
       </c>
       <c r="AW82">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX82">
         <v>20</v>
@@ -21553,7 +21553,7 @@
         <v>1.93</v>
       </c>
       <c r="G83">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="H83">
         <v>2.96</v>
@@ -21562,7 +21562,7 @@
         <v>4.2</v>
       </c>
       <c r="J83">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K83">
         <v>7</v>
@@ -21795,10 +21795,10 @@
         <v>3.1</v>
       </c>
       <c r="G84">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H84">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I84">
         <v>2.58</v>
@@ -21822,7 +21822,7 @@
         <v>0</v>
       </c>
       <c r="P84">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -22521,19 +22521,19 @@
         <v>3.7</v>
       </c>
       <c r="G87">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H87">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="I87">
         <v>2.08</v>
       </c>
       <c r="J87">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K87">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="L87">
         <v>1.01</v>
@@ -22569,7 +22569,7 @@
         <v>1.92</v>
       </c>
       <c r="W87">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X87">
         <v>1000</v>
@@ -22760,22 +22760,22 @@
         <v>393</v>
       </c>
       <c r="F88">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G88">
         <v>3.8</v>
       </c>
       <c r="H88">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I88">
         <v>3.55</v>
       </c>
       <c r="J88">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K88">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -23005,16 +23005,16 @@
         <v>2.82</v>
       </c>
       <c r="G89">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H89">
         <v>2.66</v>
       </c>
       <c r="I89">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="J89">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K89">
         <v>3.5</v>
@@ -23032,7 +23032,7 @@
         <v>0</v>
       </c>
       <c r="P89">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q89">
         <v>1.98</v>
@@ -23247,16 +23247,16 @@
         <v>2.18</v>
       </c>
       <c r="G90">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="H90">
         <v>2.94</v>
       </c>
       <c r="I90">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="J90">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K90">
         <v>5</v>
@@ -23970,19 +23970,19 @@
         <v>398</v>
       </c>
       <c r="F93">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G93">
         <v>5</v>
       </c>
       <c r="H93">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I93">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J93">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K93">
         <v>4.4</v>
@@ -24003,7 +24003,7 @@
         <v>2.4</v>
       </c>
       <c r="Q93">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -24454,22 +24454,22 @@
         <v>400</v>
       </c>
       <c r="F95">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="G95">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="H95">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="I95">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="J95">
         <v>5</v>
       </c>
       <c r="K95">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -24750,43 +24750,43 @@
         <v>0</v>
       </c>
       <c r="X96">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y96">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z96">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA96">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB96">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC96">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD96">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE96">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF96">
+        <v>13</v>
+      </c>
+      <c r="AG96">
         <v>12.5</v>
       </c>
-      <c r="AG96">
-        <v>12</v>
-      </c>
       <c r="AH96">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI96">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ96">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AK96">
         <v>19.5</v>
@@ -24795,67 +24795,67 @@
         <v>38</v>
       </c>
       <c r="AM96">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN96">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO96">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP96">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="AQ96">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AR96">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AS96">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT96">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU96">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV96">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="AW96">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="AX96">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY96">
         <v>8.6</v>
       </c>
       <c r="AZ96">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="BA96">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="BB96">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="BC96">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD96">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="BE96">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF96">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="BG96">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="BH96">
         <v>0</v>
@@ -24950,10 +24950,10 @@
         <v>3.9</v>
       </c>
       <c r="J97">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K97">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -25210,10 +25210,10 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q98">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -25428,7 +25428,7 @@
         <v>3.15</v>
       </c>
       <c r="H99">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I99">
         <v>3.1</v>
@@ -25664,16 +25664,16 @@
         <v>405</v>
       </c>
       <c r="F100">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
       <c r="G100">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H100">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="I100">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J100">
         <v>3.3</v>
@@ -26148,7 +26148,7 @@
         <v>407</v>
       </c>
       <c r="F102">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G102">
         <v>2.18</v>
@@ -26175,7 +26175,7 @@
         <v>3.1</v>
       </c>
       <c r="O102">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P102">
         <v>1.7</v>
@@ -26250,7 +26250,7 @@
         <v>140</v>
       </c>
       <c r="AN102">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO102">
         <v>80</v>
@@ -26277,7 +26277,7 @@
         <v>15.5</v>
       </c>
       <c r="AW102">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AX102">
         <v>11</v>
@@ -26393,7 +26393,7 @@
         <v>2.52</v>
       </c>
       <c r="G103">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="H103">
         <v>3.1</v>
@@ -26632,7 +26632,7 @@
         <v>409</v>
       </c>
       <c r="F104">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G104">
         <v>4.2</v>
@@ -26647,7 +26647,7 @@
         <v>3.4</v>
       </c>
       <c r="K104">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -26874,10 +26874,10 @@
         <v>410</v>
       </c>
       <c r="F105">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="G105">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H105">
         <v>5.3</v>
@@ -26886,10 +26886,10 @@
         <v>1000</v>
       </c>
       <c r="J105">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="K105">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -27358,19 +27358,19 @@
         <v>412</v>
       </c>
       <c r="F107">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="G107">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H107">
         <v>4.8</v>
       </c>
       <c r="I107">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J107">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K107">
         <v>4.2</v>
@@ -27600,22 +27600,22 @@
         <v>413</v>
       </c>
       <c r="F108">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G108">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H108">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I108">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J108">
         <v>2.96</v>
       </c>
       <c r="K108">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -27842,22 +27842,22 @@
         <v>414</v>
       </c>
       <c r="F109">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G109">
         <v>2.3</v>
       </c>
       <c r="H109">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I109">
         <v>3.95</v>
       </c>
       <c r="J109">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K109">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L109">
         <v>0</v>
@@ -27872,10 +27872,10 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q109">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -28090,13 +28090,13 @@
         <v>3.85</v>
       </c>
       <c r="H110">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I110">
         <v>2.18</v>
       </c>
       <c r="J110">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K110">
         <v>3.9</v>
@@ -28114,10 +28114,10 @@
         <v>0</v>
       </c>
       <c r="P110">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q110">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -28568,13 +28568,13 @@
         <v>417</v>
       </c>
       <c r="F112">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G112">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H112">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I112">
         <v>3.05</v>
@@ -28583,7 +28583,7 @@
         <v>2.74</v>
       </c>
       <c r="K112">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L112">
         <v>0</v>
@@ -29542,13 +29542,13 @@
         <v>1.99</v>
       </c>
       <c r="H116">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I116">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J116">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K116">
         <v>4.2</v>
@@ -29778,7 +29778,7 @@
         <v>422</v>
       </c>
       <c r="F117">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="G117">
         <v>3.5</v>
@@ -29793,7 +29793,7 @@
         <v>2.98</v>
       </c>
       <c r="K117">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L117">
         <v>0</v>
@@ -29811,7 +29811,7 @@
         <v>1.47</v>
       </c>
       <c r="Q117">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -30507,7 +30507,7 @@
         <v>1.67</v>
       </c>
       <c r="G120">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H120">
         <v>5.1</v>
@@ -30534,7 +30534,7 @@
         <v>0</v>
       </c>
       <c r="P120">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
       <c r="Q120">
         <v>2.14</v>
@@ -31236,7 +31236,7 @@
         <v>2.62</v>
       </c>
       <c r="H123">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I123">
         <v>3.4</v>
@@ -31496,19 +31496,19 @@
         <v>1.01</v>
       </c>
       <c r="N124">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O124">
         <v>1.34</v>
       </c>
       <c r="P124">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Q124">
         <v>1.84</v>
       </c>
       <c r="R124">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S124">
         <v>3.3</v>
@@ -31720,7 +31720,7 @@
         <v>1.36</v>
       </c>
       <c r="H125">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I125">
         <v>11</v>
@@ -31744,7 +31744,7 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="Q125">
         <v>1.51</v>
@@ -32198,7 +32198,7 @@
         <v>432</v>
       </c>
       <c r="F127">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G127">
         <v>1.94</v>
@@ -32207,7 +32207,7 @@
         <v>4.7</v>
       </c>
       <c r="I127">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J127">
         <v>3.55</v>
@@ -32222,22 +32222,22 @@
         <v>1.07</v>
       </c>
       <c r="N127">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O127">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P127">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q127">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R127">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S127">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="T127">
         <v>1.01</v>
@@ -32252,13 +32252,13 @@
         <v>2.06</v>
       </c>
       <c r="X127">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y127">
         <v>23</v>
       </c>
       <c r="Z127">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA127">
         <v>1000</v>
@@ -32267,7 +32267,7 @@
         <v>12</v>
       </c>
       <c r="AC127">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD127">
         <v>29</v>
@@ -32282,7 +32282,7 @@
         <v>15</v>
       </c>
       <c r="AH127">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI127">
         <v>100</v>
@@ -32300,64 +32300,64 @@
         <v>1000</v>
       </c>
       <c r="AN127">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO127">
         <v>1000</v>
       </c>
       <c r="AP127">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AQ127">
-        <v>2.42</v>
+        <v>1.86</v>
       </c>
       <c r="AR127">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="AS127">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AT127">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AU127">
-        <v>5.3</v>
+        <v>1.75</v>
       </c>
       <c r="AV127">
-        <v>2.46</v>
+        <v>1.9</v>
       </c>
       <c r="AW127">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="AX127">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AY127">
-        <v>6.4</v>
+        <v>1.79</v>
       </c>
       <c r="AZ127">
-        <v>2.46</v>
+        <v>1.9</v>
       </c>
       <c r="BA127">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="BB127">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="BC127">
-        <v>12.5</v>
+        <v>1.9</v>
       </c>
       <c r="BD127">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BE127">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="BF127">
-        <v>2.38</v>
+        <v>8.4</v>
       </c>
       <c r="BG127">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="BH127">
         <v>1000</v>
@@ -32440,16 +32440,16 @@
         <v>433</v>
       </c>
       <c r="F128">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="G128">
         <v>2.12</v>
       </c>
       <c r="H128">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I128">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J128">
         <v>3.5</v>
@@ -32682,7 +32682,7 @@
         <v>434</v>
       </c>
       <c r="F129">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="G129">
         <v>3.2</v>
@@ -32697,7 +32697,7 @@
         <v>3.2</v>
       </c>
       <c r="K129">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L129">
         <v>0</v>
@@ -32712,7 +32712,7 @@
         <v>0</v>
       </c>
       <c r="P129">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q129">
         <v>1.87</v>
@@ -32933,7 +32933,7 @@
         <v>1.82</v>
       </c>
       <c r="I130">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="J130">
         <v>3.7</v>
@@ -33656,7 +33656,7 @@
         <v>1.85</v>
       </c>
       <c r="H133">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="I133">
         <v>1000</v>
@@ -33665,7 +33665,7 @@
         <v>2.16</v>
       </c>
       <c r="K133">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -33892,22 +33892,22 @@
         <v>439</v>
       </c>
       <c r="F134">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="G134">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="H134">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="I134">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="J134">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="K134">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="L134">
         <v>0</v>
@@ -33922,7 +33922,7 @@
         <v>0</v>
       </c>
       <c r="P134">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q134">
         <v>2.06</v>
@@ -34134,10 +34134,10 @@
         <v>440</v>
       </c>
       <c r="F135">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G135">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H135">
         <v>5.7</v>
@@ -34146,7 +34146,7 @@
         <v>6.6</v>
       </c>
       <c r="J135">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K135">
         <v>4.1</v>
@@ -34164,7 +34164,7 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q135">
         <v>2.02</v>
@@ -34391,7 +34391,7 @@
         <v>3.55</v>
       </c>
       <c r="K136">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L136">
         <v>0</v>
@@ -34618,7 +34618,7 @@
         <v>442</v>
       </c>
       <c r="F137">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="G137">
         <v>1.79</v>
@@ -34627,13 +34627,13 @@
         <v>5.2</v>
       </c>
       <c r="I137">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J137">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="K137">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -34872,10 +34872,10 @@
         <v>1000</v>
       </c>
       <c r="J138">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K138">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="L138">
         <v>0</v>
@@ -35386,10 +35386,10 @@
         <v>0</v>
       </c>
       <c r="T140">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U140">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V140">
         <v>0</v>
@@ -35452,37 +35452,37 @@
         <v>16.5</v>
       </c>
       <c r="AP140">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ140">
         <v>6</v>
       </c>
       <c r="AR140">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS140">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AT140">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU140">
         <v>6.6</v>
       </c>
       <c r="AV140">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AW140">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX140">
         <v>4.6</v>
       </c>
       <c r="AY140">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AZ140">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA140">
         <v>4.6</v>
@@ -35503,7 +35503,7 @@
         <v>5</v>
       </c>
       <c r="BG140">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH140">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-16.xlsx
@@ -1366,7 +1366,7 @@
     <t>Universitario de Deportes</t>
   </si>
   <si>
-    <t>2026-08-14 17:29:29</t>
+    <t>2026-08-14 19:54:01</t>
   </si>
 </sst>
 </file>
@@ -1963,7 +1963,7 @@
         <v>1.73</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H2">
         <v>5.5</v>
@@ -1975,7 +1975,7 @@
         <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1990,7 +1990,7 @@
         <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q2">
         <v>2.02</v>
@@ -2011,19 +2011,19 @@
         <v>1.2</v>
       </c>
       <c r="W2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
         <v>18.5</v>
       </c>
       <c r="Z2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB2">
         <v>8.4</v>
@@ -2032,13 +2032,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE2">
         <v>90</v>
       </c>
       <c r="AF2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -2050,16 +2050,16 @@
         <v>90</v>
       </c>
       <c r="AJ2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL2">
         <v>46</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN2">
         <v>12.5</v>
@@ -2071,25 +2071,25 @@
         <v>12</v>
       </c>
       <c r="AQ2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AS2">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV2">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AW2">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX2">
         <v>9.199999999999999</v>
@@ -2098,28 +2098,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BF2">
         <v>10.5</v>
       </c>
       <c r="BG2">
-        <v>8.800000000000001</v>
+        <v>80</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -2244,10 +2244,10 @@
         <v>3.1</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V3">
         <v>1.26</v>
@@ -2689,7 +2689,7 @@
         <v>4.3</v>
       </c>
       <c r="G5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H5">
         <v>2.18</v>
@@ -2731,10 +2731,10 @@
         <v>2.36</v>
       </c>
       <c r="U5">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W5">
         <v>1.27</v>
@@ -2782,13 +2782,13 @@
         <v>1000</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AM5">
         <v>280</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AO5">
         <v>65</v>
@@ -2806,10 +2806,10 @@
         <v>18.5</v>
       </c>
       <c r="AT5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
         <v>11</v>
@@ -2943,7 +2943,7 @@
         <v>6.4</v>
       </c>
       <c r="K6">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="L6">
         <v>1.21</v>
@@ -3015,13 +3015,13 @@
         <v>60</v>
       </c>
       <c r="AI6">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AJ6">
         <v>8.800000000000001</v>
       </c>
       <c r="AK6">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL6">
         <v>70</v>
@@ -3039,13 +3039,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
         <v>6.8</v>
@@ -3054,10 +3054,10 @@
         <v>13.5</v>
       </c>
       <c r="AV6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX6">
         <v>5.9</v>
@@ -3066,10 +3066,10 @@
         <v>10</v>
       </c>
       <c r="AZ6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB6">
         <v>7.2</v>
@@ -3078,16 +3078,16 @@
         <v>13</v>
       </c>
       <c r="BD6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF6">
         <v>4</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -3173,19 +3173,19 @@
         <v>2.56</v>
       </c>
       <c r="G7">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H7">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I7">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J7">
         <v>3.8</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
         <v>1.26</v>
@@ -3200,7 +3200,7 @@
         <v>1.17</v>
       </c>
       <c r="P7">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q7">
         <v>1.52</v>
@@ -3215,7 +3215,7 @@
         <v>1.48</v>
       </c>
       <c r="U7">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="V7">
         <v>1.54</v>
@@ -3254,7 +3254,7 @@
         <v>13</v>
       </c>
       <c r="AH7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -3275,10 +3275,10 @@
         <v>12</v>
       </c>
       <c r="AO7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ7">
         <v>16.5</v>
@@ -3299,7 +3299,7 @@
         <v>12</v>
       </c>
       <c r="AW7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX7">
         <v>19</v>
@@ -3320,7 +3320,7 @@
         <v>20</v>
       </c>
       <c r="BD7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE7">
         <v>29</v>
@@ -3412,10 +3412,10 @@
         <v>316</v>
       </c>
       <c r="F8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G8">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H8">
         <v>4.6</v>
@@ -3436,7 +3436,7 @@
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O8">
         <v>1.24</v>
@@ -3445,25 +3445,25 @@
         <v>2.3</v>
       </c>
       <c r="Q8">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R8">
         <v>1.51</v>
       </c>
       <c r="S8">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U8">
         <v>2.32</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X8">
         <v>21</v>
@@ -3472,7 +3472,7 @@
         <v>21</v>
       </c>
       <c r="Z8">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -3484,28 +3484,28 @@
         <v>9.6</v>
       </c>
       <c r="AD8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE8">
-        <v>350</v>
+        <v>270</v>
       </c>
       <c r="AF8">
         <v>12.5</v>
       </c>
       <c r="AG8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
         <v>19</v>
       </c>
       <c r="AI8">
-        <v>400</v>
+        <v>310</v>
       </c>
       <c r="AJ8">
         <v>19.5</v>
       </c>
       <c r="AK8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL8">
         <v>32</v>
@@ -3517,19 +3517,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO8">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AP8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ8">
         <v>17.5</v>
       </c>
       <c r="AR8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT8">
         <v>9.800000000000001</v>
@@ -3550,10 +3550,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB8">
         <v>16.5</v>
@@ -3571,7 +3571,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3666,7 +3666,7 @@
         <v>6.4</v>
       </c>
       <c r="J9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K9">
         <v>5.2</v>
@@ -3678,16 +3678,16 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O9">
         <v>1.19</v>
       </c>
       <c r="P9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q9">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R9">
         <v>1.64</v>
@@ -3896,22 +3896,22 @@
         <v>318</v>
       </c>
       <c r="F10">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G10">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="H10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L10">
         <v>1.3</v>
@@ -3929,7 +3929,7 @@
         <v>2.48</v>
       </c>
       <c r="Q10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R10">
         <v>1.6</v>
@@ -3947,28 +3947,28 @@
         <v>1.25</v>
       </c>
       <c r="W10">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y10">
         <v>25</v>
       </c>
       <c r="Z10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA10">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
         <v>12.5</v>
       </c>
       <c r="AC10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE10">
         <v>55</v>
@@ -3977,19 +3977,19 @@
         <v>12.5</v>
       </c>
       <c r="AG10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI10">
         <v>55</v>
       </c>
       <c r="AJ10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL10">
         <v>27</v>
@@ -3998,19 +3998,19 @@
         <v>75</v>
       </c>
       <c r="AN10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO10">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP10">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AQ10">
         <v>21</v>
       </c>
       <c r="AR10">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AS10">
         <v>38</v>
@@ -4019,10 +4019,10 @@
         <v>11</v>
       </c>
       <c r="AU10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW10">
         <v>40</v>
@@ -4037,7 +4037,7 @@
         <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB10">
         <v>17</v>
@@ -4052,7 +4052,7 @@
         <v>32</v>
       </c>
       <c r="BF10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG10">
         <v>30</v>
@@ -4138,7 +4138,7 @@
         <v>319</v>
       </c>
       <c r="F11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G11">
         <v>1.55</v>
@@ -4150,10 +4150,10 @@
         <v>6.8</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K11">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L11">
         <v>1.26</v>
@@ -4189,7 +4189,7 @@
         <v>1.17</v>
       </c>
       <c r="W11">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X11">
         <v>34</v>
@@ -4198,7 +4198,7 @@
         <v>36</v>
       </c>
       <c r="Z11">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -4207,7 +4207,7 @@
         <v>13</v>
       </c>
       <c r="AC11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD11">
         <v>29</v>
@@ -4222,10 +4222,10 @@
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI11">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="AJ11">
         <v>15.5</v>
@@ -4243,10 +4243,10 @@
         <v>5.3</v>
       </c>
       <c r="AO11">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="AP11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ11">
         <v>25</v>
@@ -4267,7 +4267,7 @@
         <v>18.5</v>
       </c>
       <c r="AW11">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AX11">
         <v>10</v>
@@ -4276,13 +4276,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA11">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC11">
         <v>12.5</v>
@@ -4291,10 +4291,10 @@
         <v>21</v>
       </c>
       <c r="BE11">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG11">
         <v>30</v>
@@ -4380,166 +4380,166 @@
         <v>320</v>
       </c>
       <c r="F12">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="G12">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="H12">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="I12">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="J12">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P12">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q12">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
         <v>3.1</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V12">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W12">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY12">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -4622,10 +4622,10 @@
         <v>321</v>
       </c>
       <c r="F13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G13">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H13">
         <v>5.1</v>
@@ -4643,7 +4643,7 @@
         <v>1.26</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
         <v>6.6</v>
@@ -4673,7 +4673,7 @@
         <v>1.22</v>
       </c>
       <c r="W13">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X13">
         <v>32</v>
@@ -4691,7 +4691,7 @@
         <v>14</v>
       </c>
       <c r="AC13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD13">
         <v>24</v>
@@ -4715,13 +4715,13 @@
         <v>20</v>
       </c>
       <c r="AK13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL13">
         <v>25</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="AN13">
         <v>6</v>
@@ -4736,7 +4736,7 @@
         <v>19</v>
       </c>
       <c r="AR13">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AS13">
         <v>40</v>
@@ -4864,16 +4864,16 @@
         <v>322</v>
       </c>
       <c r="F14">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G14">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H14">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J14">
         <v>3.95</v>
@@ -4912,10 +4912,10 @@
         <v>2.82</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X14">
         <v>27</v>
@@ -4927,7 +4927,7 @@
         <v>28</v>
       </c>
       <c r="AA14">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB14">
         <v>16.5</v>
@@ -4942,7 +4942,7 @@
         <v>30</v>
       </c>
       <c r="AF14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG14">
         <v>12</v>
@@ -4954,10 +4954,10 @@
         <v>34</v>
       </c>
       <c r="AJ14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL14">
         <v>27</v>
@@ -4969,7 +4969,7 @@
         <v>10.5</v>
       </c>
       <c r="AO14">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP14">
         <v>22</v>
@@ -4990,7 +4990,7 @@
         <v>9</v>
       </c>
       <c r="AV14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW14">
         <v>26</v>
@@ -5005,7 +5005,7 @@
         <v>12.5</v>
       </c>
       <c r="BA14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB14">
         <v>26</v>
@@ -5023,7 +5023,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -5112,7 +5112,7 @@
         <v>3.8</v>
       </c>
       <c r="H15">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I15">
         <v>2.32</v>
@@ -5121,151 +5121,151 @@
         <v>3.35</v>
       </c>
       <c r="K15">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O15">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P15">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q15">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R15">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S15">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="T15">
         <v>1.87</v>
       </c>
       <c r="U15">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V15">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W15">
         <v>1.35</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z15">
         <v>14</v>
       </c>
-      <c r="Z15">
+      <c r="AA15">
+        <v>38</v>
+      </c>
+      <c r="AB15">
         <v>15</v>
       </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
       <c r="AC15">
+        <v>7.8</v>
+      </c>
+      <c r="AD15">
+        <v>13.5</v>
+      </c>
+      <c r="AE15">
+        <v>32</v>
+      </c>
+      <c r="AF15">
+        <v>32</v>
+      </c>
+      <c r="AG15">
+        <v>16</v>
+      </c>
+      <c r="AH15">
+        <v>24</v>
+      </c>
+      <c r="AI15">
+        <v>55</v>
+      </c>
+      <c r="AJ15">
+        <v>90</v>
+      </c>
+      <c r="AK15">
+        <v>60</v>
+      </c>
+      <c r="AL15">
+        <v>75</v>
+      </c>
+      <c r="AM15">
+        <v>150</v>
+      </c>
+      <c r="AN15">
+        <v>70</v>
+      </c>
+      <c r="AO15">
+        <v>27</v>
+      </c>
+      <c r="AP15">
+        <v>10.5</v>
+      </c>
+      <c r="AQ15">
+        <v>7.8</v>
+      </c>
+      <c r="AR15">
+        <v>12</v>
+      </c>
+      <c r="AS15">
+        <v>5.6</v>
+      </c>
+      <c r="AT15">
         <v>11</v>
       </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>28</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.36</v>
-      </c>
-      <c r="AQ15">
-        <v>1.23</v>
-      </c>
-      <c r="AR15">
-        <v>1.24</v>
-      </c>
-      <c r="AS15">
-        <v>1.36</v>
-      </c>
-      <c r="AT15">
-        <v>1.36</v>
-      </c>
       <c r="AU15">
-        <v>1.21</v>
+        <v>6.8</v>
       </c>
       <c r="AV15">
-        <v>1.36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15">
-        <v>1.36</v>
+        <v>5.6</v>
       </c>
       <c r="AX15">
-        <v>1.36</v>
+        <v>5.6</v>
       </c>
       <c r="AY15">
-        <v>1.36</v>
+        <v>13.5</v>
       </c>
       <c r="AZ15">
-        <v>1.29</v>
+        <v>16.5</v>
       </c>
       <c r="BA15">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="BB15">
-        <v>1.36</v>
+        <v>6.2</v>
       </c>
       <c r="BC15">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="BD15">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="BE15">
-        <v>1.36</v>
+        <v>6.4</v>
       </c>
       <c r="BF15">
-        <v>1.36</v>
+        <v>6.2</v>
       </c>
       <c r="BG15">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -5384,7 +5384,7 @@
         <v>1.7</v>
       </c>
       <c r="R16">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="S16">
         <v>2.74</v>
@@ -5593,7 +5593,7 @@
         <v>1.9</v>
       </c>
       <c r="G17">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H17">
         <v>3.35</v>
@@ -5605,7 +5605,7 @@
         <v>3.1</v>
       </c>
       <c r="K17">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L17">
         <v>1.34</v>
@@ -5614,7 +5614,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O17">
         <v>1.37</v>
@@ -5641,7 +5641,7 @@
         <v>1.22</v>
       </c>
       <c r="W17">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -6086,10 +6086,10 @@
         <v>3.75</v>
       </c>
       <c r="J19">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K19">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L19">
         <v>1.44</v>
@@ -6101,7 +6101,7 @@
         <v>2.46</v>
       </c>
       <c r="O19">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P19">
         <v>1.44</v>
@@ -6316,7 +6316,7 @@
         <v>328</v>
       </c>
       <c r="F20">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="G20">
         <v>4.8</v>
@@ -6325,13 +6325,13 @@
         <v>1.97</v>
       </c>
       <c r="I20">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J20">
         <v>2.92</v>
       </c>
       <c r="K20">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -6346,16 +6346,16 @@
         <v>1.34</v>
       </c>
       <c r="P20">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Q20">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="R20">
         <v>1.24</v>
       </c>
       <c r="S20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -6364,10 +6364,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -6600,7 +6600,7 @@
         <v>2.6</v>
       </c>
       <c r="T21">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U21">
         <v>2.42</v>
@@ -6806,7 +6806,7 @@
         <v>2.3</v>
       </c>
       <c r="H22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I22">
         <v>4.3</v>
@@ -6839,7 +6839,7 @@
         <v>1.18</v>
       </c>
       <c r="S22">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6848,7 +6848,7 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W22">
         <v>1.77</v>
@@ -6911,49 +6911,49 @@
         <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -7072,7 +7072,7 @@
         <v>1.33</v>
       </c>
       <c r="P23">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q23">
         <v>1.96</v>
@@ -7084,13 +7084,13 @@
         <v>3.5</v>
       </c>
       <c r="T23">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U23">
         <v>2.16</v>
       </c>
       <c r="V23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
         <v>1.52</v>
@@ -7114,7 +7114,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD23">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE23">
         <v>38</v>
@@ -7123,7 +7123,7 @@
         <v>23</v>
       </c>
       <c r="AG23">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH23">
         <v>21</v>
@@ -7141,7 +7141,7 @@
         <v>55</v>
       </c>
       <c r="AM23">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN23">
         <v>34</v>
@@ -7159,7 +7159,7 @@
         <v>13.5</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT23">
         <v>10</v>
@@ -7171,10 +7171,10 @@
         <v>11</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX23">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AY23">
         <v>11</v>
@@ -7183,19 +7183,19 @@
         <v>13</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF23">
         <v>19.5</v>
@@ -7299,7 +7299,7 @@
         <v>3.35</v>
       </c>
       <c r="K24">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L24">
         <v>1.33</v>
@@ -7308,7 +7308,7 @@
         <v>1.04</v>
       </c>
       <c r="N24">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O24">
         <v>1.35</v>
@@ -7317,7 +7317,7 @@
         <v>1.82</v>
       </c>
       <c r="Q24">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R24">
         <v>1.32</v>
@@ -7335,13 +7335,13 @@
         <v>2.1</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X24">
         <v>1000</v>
       </c>
       <c r="Y24">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
         <v>19.5</v>
@@ -7353,7 +7353,7 @@
         <v>1000</v>
       </c>
       <c r="AC24">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
         <v>19</v>
@@ -7392,58 +7392,58 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -8019,7 +8019,7 @@
         <v>2.62</v>
       </c>
       <c r="I27">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J27">
         <v>3.55</v>
@@ -8043,13 +8043,13 @@
         <v>2.08</v>
       </c>
       <c r="Q27">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="R27">
         <v>1.41</v>
       </c>
       <c r="S27">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="T27">
         <v>1.01</v>
@@ -8252,19 +8252,19 @@
         <v>336</v>
       </c>
       <c r="F28">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="G28">
+        <v>3.8</v>
+      </c>
+      <c r="H28">
+        <v>2.12</v>
+      </c>
+      <c r="I28">
+        <v>2.22</v>
+      </c>
+      <c r="J28">
         <v>3.7</v>
-      </c>
-      <c r="H28">
-        <v>2.14</v>
-      </c>
-      <c r="I28">
-        <v>2.26</v>
-      </c>
-      <c r="J28">
-        <v>3.65</v>
       </c>
       <c r="K28">
         <v>3.85</v>
@@ -8297,16 +8297,16 @@
         <v>1.71</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V28">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W28">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X28">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y28">
         <v>11</v>
@@ -8327,13 +8327,13 @@
         <v>11</v>
       </c>
       <c r="AE28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF28">
         <v>32</v>
       </c>
       <c r="AG28">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH28">
         <v>17</v>
@@ -8357,7 +8357,7 @@
         <v>42</v>
       </c>
       <c r="AO28">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP28">
         <v>14.5</v>
@@ -8369,10 +8369,10 @@
         <v>13</v>
       </c>
       <c r="AS28">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AT28">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AU28">
         <v>7.6</v>
@@ -8384,19 +8384,19 @@
         <v>19.5</v>
       </c>
       <c r="AX28">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AY28">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ28">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA28">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB28">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC28">
         <v>32</v>
@@ -8405,10 +8405,10 @@
         <v>36</v>
       </c>
       <c r="BE28">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF28">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG28">
         <v>11</v>
@@ -8993,7 +8993,7 @@
         <v>3.65</v>
       </c>
       <c r="K31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -9546,7 +9546,7 @@
         <v>1000</v>
       </c>
       <c r="AH33">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI33">
         <v>1000</v>
@@ -9570,58 +9570,58 @@
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AQ33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AR33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AS33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AT33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AU33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AV33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AW33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AX33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AY33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AZ33">
         <v>1.17</v>
       </c>
       <c r="BA33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BB33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BC33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BD33">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="BE33">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BF33">
         <v>5.9</v>
       </c>
       <c r="BG33">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9704,13 +9704,13 @@
         <v>342</v>
       </c>
       <c r="F34">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G34">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H34">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I34">
         <v>6.2</v>
@@ -9725,16 +9725,16 @@
         <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N34">
         <v>5.7</v>
       </c>
       <c r="O34">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P34">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q34">
         <v>1.56</v>
@@ -9755,10 +9755,10 @@
         <v>1.19</v>
       </c>
       <c r="W34">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X34">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y34">
         <v>28</v>
@@ -9767,7 +9767,7 @@
         <v>55</v>
       </c>
       <c r="AA34">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AB34">
         <v>13</v>
@@ -9776,19 +9776,19 @@
         <v>11.5</v>
       </c>
       <c r="AD34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE34">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AF34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG34">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH34">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI34">
         <v>65</v>
@@ -9797,73 +9797,73 @@
         <v>16.5</v>
       </c>
       <c r="AK34">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL34">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM34">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN34">
         <v>6.2</v>
       </c>
       <c r="AO34">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP34">
         <v>21</v>
       </c>
       <c r="AQ34">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AR34">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="AS34">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT34">
+        <v>11</v>
+      </c>
+      <c r="AU34">
+        <v>10</v>
+      </c>
+      <c r="AV34">
+        <v>20</v>
+      </c>
+      <c r="AW34">
+        <v>55</v>
+      </c>
+      <c r="AX34">
         <v>10.5</v>
       </c>
-      <c r="AU34">
+      <c r="AY34">
         <v>9.4</v>
       </c>
-      <c r="AV34">
-        <v>19</v>
-      </c>
-      <c r="AW34">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX34">
+      <c r="AZ34">
+        <v>16.5</v>
+      </c>
+      <c r="BA34">
+        <v>50</v>
+      </c>
+      <c r="BB34">
+        <v>14.5</v>
+      </c>
+      <c r="BC34">
+        <v>13.5</v>
+      </c>
+      <c r="BD34">
+        <v>23</v>
+      </c>
+      <c r="BE34">
         <v>10</v>
       </c>
-      <c r="AY34">
-        <v>9</v>
-      </c>
-      <c r="AZ34">
-        <v>15.5</v>
-      </c>
-      <c r="BA34">
-        <v>40</v>
-      </c>
-      <c r="BB34">
-        <v>13</v>
-      </c>
-      <c r="BC34">
-        <v>13</v>
-      </c>
-      <c r="BD34">
-        <v>19</v>
-      </c>
-      <c r="BE34">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF34">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9949,7 +9949,7 @@
         <v>1.84</v>
       </c>
       <c r="G35">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H35">
         <v>4.1</v>
@@ -9997,7 +9997,7 @@
         <v>1.28</v>
       </c>
       <c r="W35">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X35">
         <v>32</v>
@@ -10203,7 +10203,7 @@
         <v>3.5</v>
       </c>
       <c r="K36">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -10215,7 +10215,7 @@
         <v>3.6</v>
       </c>
       <c r="O36">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P36">
         <v>1.99</v>
@@ -10224,19 +10224,19 @@
         <v>1.92</v>
       </c>
       <c r="R36">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S36">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="T36">
         <v>1.66</v>
       </c>
       <c r="U36">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V36">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W36">
         <v>1.44</v>
@@ -10472,7 +10472,7 @@
         <v>1.96</v>
       </c>
       <c r="T37">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="U37">
         <v>2.42</v>
@@ -10696,7 +10696,7 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O38">
         <v>1.18</v>
@@ -10929,7 +10929,7 @@
         <v>3.85</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L39">
         <v>1.01</v>
@@ -10944,7 +10944,7 @@
         <v>1.37</v>
       </c>
       <c r="P39">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q39">
         <v>2.1</v>
@@ -10953,19 +10953,19 @@
         <v>1.31</v>
       </c>
       <c r="S39">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T39">
         <v>2.02</v>
       </c>
       <c r="U39">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="V39">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W39">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X39">
         <v>12.5</v>
@@ -10983,7 +10983,7 @@
         <v>7.6</v>
       </c>
       <c r="AC39">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD39">
         <v>28</v>
@@ -11001,7 +11001,7 @@
         <v>24</v>
       </c>
       <c r="AI39">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ39">
         <v>18.5</v>
@@ -11031,7 +11031,7 @@
         <v>36</v>
       </c>
       <c r="AS39">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AT39">
         <v>6.8</v>
@@ -11043,7 +11043,7 @@
         <v>20</v>
       </c>
       <c r="AW39">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX39">
         <v>8.4</v>
@@ -11055,25 +11055,25 @@
         <v>21</v>
       </c>
       <c r="BA39">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BB39">
         <v>17</v>
       </c>
       <c r="BC39">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD39">
         <v>38</v>
       </c>
       <c r="BE39">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BF39">
         <v>11.5</v>
       </c>
       <c r="BG39">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -11159,16 +11159,16 @@
         <v>1.24</v>
       </c>
       <c r="G40">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H40">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="I40">
         <v>15.5</v>
       </c>
       <c r="J40">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K40">
         <v>8</v>
@@ -11180,13 +11180,13 @@
         <v>1.02</v>
       </c>
       <c r="N40">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>1.11</v>
       </c>
       <c r="P40">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q40">
         <v>1.39</v>
@@ -11195,7 +11195,7 @@
         <v>1.92</v>
       </c>
       <c r="S40">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T40">
         <v>1.84</v>
@@ -11207,7 +11207,7 @@
         <v>1.06</v>
       </c>
       <c r="W40">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="X40">
         <v>55</v>
@@ -11219,19 +11219,19 @@
         <v>170</v>
       </c>
       <c r="AA40">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="AB40">
         <v>14</v>
       </c>
       <c r="AC40">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AD40">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE40">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF40">
         <v>11</v>
@@ -11240,10 +11240,10 @@
         <v>12</v>
       </c>
       <c r="AH40">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI40">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ40">
         <v>11.5</v>
@@ -11261,19 +11261,19 @@
         <v>3.45</v>
       </c>
       <c r="AO40">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP40">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ40">
         <v>32</v>
       </c>
       <c r="AR40">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS40">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT40">
         <v>11</v>
@@ -11285,7 +11285,7 @@
         <v>27</v>
       </c>
       <c r="AW40">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX40">
         <v>8.800000000000001</v>
@@ -11297,7 +11297,7 @@
         <v>16.5</v>
       </c>
       <c r="BA40">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB40">
         <v>9.199999999999999</v>
@@ -11306,16 +11306,16 @@
         <v>11</v>
       </c>
       <c r="BD40">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE40">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF40">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BG40">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -11398,16 +11398,16 @@
         <v>349</v>
       </c>
       <c r="F41">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G41">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H41">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I41">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J41">
         <v>5.7</v>
@@ -11440,7 +11440,7 @@
         <v>1.9</v>
       </c>
       <c r="T41">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U41">
         <v>2.44</v>
@@ -11449,7 +11449,7 @@
         <v>1.14</v>
       </c>
       <c r="W41">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X41">
         <v>40</v>
@@ -11458,7 +11458,7 @@
         <v>50</v>
       </c>
       <c r="Z41">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AA41">
         <v>230</v>
@@ -11467,13 +11467,13 @@
         <v>16</v>
       </c>
       <c r="AC41">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD41">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE41">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF41">
         <v>13</v>
@@ -11482,10 +11482,10 @@
         <v>11</v>
       </c>
       <c r="AH41">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI41">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ41">
         <v>14.5</v>
@@ -11512,7 +11512,7 @@
         <v>38</v>
       </c>
       <c r="AR41">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS41">
         <v>16</v>
@@ -11542,7 +11542,7 @@
         <v>40</v>
       </c>
       <c r="BB41">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC41">
         <v>12</v>
@@ -11640,10 +11640,10 @@
         <v>350</v>
       </c>
       <c r="F42">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G42">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H42">
         <v>2.16</v>
@@ -11652,10 +11652,10 @@
         <v>2.2</v>
       </c>
       <c r="J42">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K42">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L42">
         <v>1.01</v>
@@ -11673,7 +11673,7 @@
         <v>2.14</v>
       </c>
       <c r="Q42">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R42">
         <v>1.45</v>
@@ -11688,10 +11688,10 @@
         <v>2.42</v>
       </c>
       <c r="V42">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W42">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X42">
         <v>17.5</v>
@@ -11751,7 +11751,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ42">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR42">
         <v>13</v>
@@ -11790,13 +11790,13 @@
         <v>34</v>
       </c>
       <c r="BD42">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE42">
         <v>32</v>
       </c>
       <c r="BF42">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG42">
         <v>12</v>
@@ -11885,7 +11885,7 @@
         <v>2.64</v>
       </c>
       <c r="G43">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H43">
         <v>2.44</v>
@@ -11906,7 +11906,7 @@
         <v>1.02</v>
       </c>
       <c r="N43">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="O43">
         <v>1.14</v>
@@ -11918,130 +11918,130 @@
         <v>1.42</v>
       </c>
       <c r="R43">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="S43">
         <v>2.02</v>
       </c>
       <c r="T43">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U43">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="V43">
         <v>1.61</v>
       </c>
       <c r="W43">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X43">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y43">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z43">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA43">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB43">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC43">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD43">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE43">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF43">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG43">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH43">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AI43">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ43">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK43">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL43">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM43">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO43">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP43">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ43">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS43">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT43">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AU43">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW43">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ43">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA43">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB43">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC43">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD43">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE43">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG43">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH43">
         <v>1000</v>
@@ -12617,7 +12617,7 @@
         <v>2.52</v>
       </c>
       <c r="I46">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J46">
         <v>3.65</v>
@@ -12632,7 +12632,7 @@
         <v>1.03</v>
       </c>
       <c r="N46">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="O46">
         <v>1.18</v>
@@ -12641,7 +12641,7 @@
         <v>2.18</v>
       </c>
       <c r="Q46">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="R46">
         <v>1.5</v>
@@ -12653,10 +12653,10 @@
         <v>1.01</v>
       </c>
       <c r="U46">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V46">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
         <v>1.52</v>
@@ -13606,7 +13606,7 @@
         <v>1.36</v>
       </c>
       <c r="P50">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q50">
         <v>2</v>
@@ -13618,7 +13618,7 @@
         <v>3.3</v>
       </c>
       <c r="T50">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U50">
         <v>1.01</v>
@@ -13848,13 +13848,13 @@
         <v>1.35</v>
       </c>
       <c r="P51">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Q51">
         <v>2.08</v>
       </c>
       <c r="R51">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S51">
         <v>3.7</v>
@@ -13863,7 +13863,7 @@
         <v>1.79</v>
       </c>
       <c r="U51">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V51">
         <v>1.67</v>
@@ -14302,10 +14302,10 @@
         <v>361</v>
       </c>
       <c r="F53">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="G53">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H53">
         <v>2.72</v>
@@ -14320,7 +14320,7 @@
         <v>3.75</v>
       </c>
       <c r="L53">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M53">
         <v>1.05</v>
@@ -14353,7 +14353,7 @@
         <v>1.53</v>
       </c>
       <c r="W53">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X53">
         <v>1000</v>
@@ -14786,46 +14786,46 @@
         <v>363</v>
       </c>
       <c r="F55">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="G55">
+        <v>4</v>
+      </c>
+      <c r="H55">
+        <v>1.93</v>
+      </c>
+      <c r="I55">
+        <v>2.02</v>
+      </c>
+      <c r="J55">
         <v>3.9</v>
       </c>
-      <c r="H55">
-        <v>2.02</v>
-      </c>
-      <c r="I55">
-        <v>2.08</v>
-      </c>
-      <c r="J55">
-        <v>3.85</v>
-      </c>
       <c r="K55">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L55">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M55">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N55">
         <v>4.1</v>
       </c>
       <c r="O55">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P55">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q55">
         <v>1.72</v>
       </c>
       <c r="R55">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S55">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T55">
         <v>1.7</v>
@@ -14834,52 +14834,52 @@
         <v>2.24</v>
       </c>
       <c r="V55">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="W55">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X55">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y55">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z55">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA55">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AB55">
         <v>18</v>
       </c>
       <c r="AC55">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD55">
         <v>12.5</v>
       </c>
       <c r="AE55">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF55">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG55">
         <v>17.5</v>
       </c>
       <c r="AH55">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI55">
         <v>38</v>
       </c>
       <c r="AJ55">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AK55">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AL55">
         <v>55</v>
@@ -14891,7 +14891,7 @@
         <v>48</v>
       </c>
       <c r="AO55">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AP55">
         <v>13.5</v>
@@ -14906,10 +14906,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT55">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU55">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV55">
         <v>7.6</v>
@@ -14921,7 +14921,7 @@
         <v>20</v>
       </c>
       <c r="AY55">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ55">
         <v>13</v>
@@ -15052,7 +15052,7 @@
         <v>1.03</v>
       </c>
       <c r="N56">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="O56">
         <v>1.16</v>
@@ -15064,13 +15064,13 @@
         <v>1.54</v>
       </c>
       <c r="R56">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S56">
         <v>2.32</v>
       </c>
       <c r="T56">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U56">
         <v>2.32</v>
@@ -15276,7 +15276,7 @@
         <v>1.96</v>
       </c>
       <c r="H57">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I57">
         <v>6.2</v>
@@ -15303,7 +15303,7 @@
         <v>1.67</v>
       </c>
       <c r="Q57">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R57">
         <v>1.23</v>
@@ -15512,7 +15512,7 @@
         <v>366</v>
       </c>
       <c r="F58">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="G58">
         <v>4.1</v>
@@ -15521,10 +15521,10 @@
         <v>2.06</v>
       </c>
       <c r="I58">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="J58">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K58">
         <v>3.75</v>
@@ -15539,10 +15539,10 @@
         <v>3.35</v>
       </c>
       <c r="O58">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P58">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="Q58">
         <v>1.92</v>
@@ -15560,7 +15560,7 @@
         <v>1.01</v>
       </c>
       <c r="V58">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W58">
         <v>1.32</v>
@@ -15644,7 +15644,7 @@
         <v>2.56</v>
       </c>
       <c r="AX58">
-        <v>16.5</v>
+        <v>2.58</v>
       </c>
       <c r="AY58">
         <v>2.46</v>
@@ -15754,22 +15754,22 @@
         <v>367</v>
       </c>
       <c r="F59">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="G59">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H59">
         <v>2.36</v>
       </c>
       <c r="I59">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="J59">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K59">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="L59">
         <v>1.36</v>
@@ -15778,16 +15778,16 @@
         <v>1.06</v>
       </c>
       <c r="N59">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="O59">
         <v>1.3</v>
       </c>
       <c r="P59">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="Q59">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="R59">
         <v>1.29</v>
@@ -15799,13 +15799,13 @@
         <v>1.01</v>
       </c>
       <c r="U59">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V59">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="W59">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X59">
         <v>1000</v>
@@ -16271,7 +16271,7 @@
         <v>2.24</v>
       </c>
       <c r="Q61">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="R61">
         <v>1.45</v>
@@ -16280,10 +16280,10 @@
         <v>2.38</v>
       </c>
       <c r="T61">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U61">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V61">
         <v>2.06</v>
@@ -16749,7 +16749,7 @@
         <v>1.01</v>
       </c>
       <c r="O63">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P63">
         <v>2.26</v>
@@ -16964,22 +16964,22 @@
         <v>372</v>
       </c>
       <c r="F64">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G64">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="H64">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="I64">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="J64">
         <v>3.45</v>
       </c>
       <c r="K64">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="L64">
         <v>1.01</v>
@@ -16988,13 +16988,13 @@
         <v>1.01</v>
       </c>
       <c r="N64">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O64">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P64">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q64">
         <v>1.52</v>
@@ -17003,7 +17003,7 @@
         <v>1.42</v>
       </c>
       <c r="S64">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="T64">
         <v>1.01</v>
@@ -17012,10 +17012,10 @@
         <v>1.01</v>
       </c>
       <c r="V64">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="W64">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X64">
         <v>1000</v>
@@ -17215,7 +17215,7 @@
         <v>2.38</v>
       </c>
       <c r="I65">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J65">
         <v>3.6</v>
@@ -17230,13 +17230,13 @@
         <v>1.01</v>
       </c>
       <c r="N65">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="O65">
         <v>1.16</v>
       </c>
       <c r="P65">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="Q65">
         <v>1.53</v>
@@ -17254,7 +17254,7 @@
         <v>1.01</v>
       </c>
       <c r="V65">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W65">
         <v>1.46</v>
@@ -17451,7 +17451,7 @@
         <v>2.74</v>
       </c>
       <c r="G66">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H66">
         <v>2.64</v>
@@ -17460,7 +17460,7 @@
         <v>2.84</v>
       </c>
       <c r="J66">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K66">
         <v>3.65</v>
@@ -17499,7 +17499,7 @@
         <v>1.54</v>
       </c>
       <c r="W66">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X66">
         <v>18</v>
@@ -17690,7 +17690,7 @@
         <v>375</v>
       </c>
       <c r="F67">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G67">
         <v>1.52</v>
@@ -17729,13 +17729,13 @@
         <v>1.81</v>
       </c>
       <c r="S67">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T67">
         <v>1.63</v>
       </c>
       <c r="U67">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V67">
         <v>1.16</v>
@@ -17762,7 +17762,7 @@
         <v>13</v>
       </c>
       <c r="AD67">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE67">
         <v>75</v>
@@ -17819,7 +17819,7 @@
         <v>23</v>
       </c>
       <c r="AW67">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AX67">
         <v>11</v>
@@ -17977,7 +17977,7 @@
         <v>1.57</v>
       </c>
       <c r="U68">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="V68">
         <v>1.3</v>
@@ -17989,7 +17989,7 @@
         <v>1000</v>
       </c>
       <c r="Y68">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z68">
         <v>1000</v>
@@ -18010,13 +18010,13 @@
         <v>1000</v>
       </c>
       <c r="AF68">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG68">
         <v>1000</v>
       </c>
       <c r="AH68">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI68">
         <v>1000</v>
@@ -18040,58 +18040,58 @@
         <v>1000</v>
       </c>
       <c r="AP68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AQ68">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AR68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AS68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AT68">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AU68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AV68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AW68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AX68">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AY68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AZ68">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="BA68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="BB68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="BC68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="BD68">
         <v>19</v>
       </c>
       <c r="BE68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="BF68">
-        <v>6.2</v>
+        <v>1.06</v>
       </c>
       <c r="BG68">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="BH68">
         <v>1000</v>
@@ -18658,16 +18658,16 @@
         <v>379</v>
       </c>
       <c r="F71">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G71">
         <v>3.5</v>
       </c>
       <c r="H71">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I71">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J71">
         <v>3.7</v>
@@ -18685,7 +18685,7 @@
         <v>4.5</v>
       </c>
       <c r="O71">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P71">
         <v>2.2</v>
@@ -18697,16 +18697,16 @@
         <v>1.46</v>
       </c>
       <c r="S71">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T71">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U71">
         <v>2.38</v>
       </c>
       <c r="V71">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W71">
         <v>1.4</v>
@@ -18757,7 +18757,7 @@
         <v>46</v>
       </c>
       <c r="AM71">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN71">
         <v>30</v>
@@ -18790,7 +18790,7 @@
         <v>19.5</v>
       </c>
       <c r="AX71">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY71">
         <v>13</v>
@@ -18859,7 +18859,7 @@
         <v>1000</v>
       </c>
       <c r="BU71">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV71">
         <v>1000</v>
@@ -18945,7 +18945,7 @@
         <v>1.86</v>
       </c>
       <c r="U72">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="V72">
         <v>1.12</v>
@@ -19142,7 +19142,7 @@
         <v>381</v>
       </c>
       <c r="F73">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="G73">
         <v>2.3</v>
@@ -19151,13 +19151,13 @@
         <v>3.1</v>
       </c>
       <c r="I73">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J73">
         <v>3.75</v>
       </c>
       <c r="K73">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="L73">
         <v>1.01</v>
@@ -19166,19 +19166,19 @@
         <v>1.01</v>
       </c>
       <c r="N73">
-        <v>2.72</v>
+        <v>1.25</v>
       </c>
       <c r="O73">
         <v>1.14</v>
       </c>
       <c r="P73">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q73">
         <v>1.41</v>
       </c>
       <c r="R73">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="S73">
         <v>2.04</v>
@@ -19671,7 +19671,7 @@
         <v>1.59</v>
       </c>
       <c r="U75">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="V75">
         <v>1.42</v>
@@ -19868,22 +19868,22 @@
         <v>384</v>
       </c>
       <c r="F76">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G76">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H76">
+        <v>2.36</v>
+      </c>
+      <c r="I76">
         <v>2.4</v>
-      </c>
-      <c r="I76">
-        <v>2.44</v>
       </c>
       <c r="J76">
         <v>3.6</v>
       </c>
       <c r="K76">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L76">
         <v>1.01</v>
@@ -19898,7 +19898,7 @@
         <v>1.26</v>
       </c>
       <c r="P76">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q76">
         <v>1.79</v>
@@ -19916,19 +19916,19 @@
         <v>2.34</v>
       </c>
       <c r="V76">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W76">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X76">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y76">
         <v>12</v>
       </c>
       <c r="Z76">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA76">
         <v>32</v>
@@ -19970,7 +19970,7 @@
         <v>75</v>
       </c>
       <c r="AN76">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO76">
         <v>16.5</v>
@@ -19991,10 +19991,10 @@
         <v>13.5</v>
       </c>
       <c r="AU76">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV76">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW76">
         <v>19.5</v>
@@ -20003,7 +20003,7 @@
         <v>21</v>
       </c>
       <c r="AY76">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ76">
         <v>14.5</v>
@@ -20113,7 +20113,7 @@
         <v>1.89</v>
       </c>
       <c r="G77">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H77">
         <v>3.25</v>
@@ -20134,13 +20134,13 @@
         <v>1.01</v>
       </c>
       <c r="N77">
-        <v>4.6</v>
+        <v>2.32</v>
       </c>
       <c r="O77">
         <v>1.04</v>
       </c>
       <c r="P77">
-        <v>4.6</v>
+        <v>2.32</v>
       </c>
       <c r="Q77">
         <v>1.17</v>
@@ -20161,7 +20161,7 @@
         <v>1.41</v>
       </c>
       <c r="W77">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X77">
         <v>1000</v>
@@ -20361,13 +20361,13 @@
         <v>2.84</v>
       </c>
       <c r="I78">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="J78">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K78">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L78">
         <v>1.01</v>
@@ -20388,7 +20388,7 @@
         <v>1.17</v>
       </c>
       <c r="R78">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="S78">
         <v>2.42</v>
@@ -20400,7 +20400,7 @@
         <v>1.01</v>
       </c>
       <c r="V78">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W78">
         <v>1.66</v>
@@ -21344,7 +21344,7 @@
         <v>1.06</v>
       </c>
       <c r="N82">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="O82">
         <v>1.35</v>
@@ -21353,7 +21353,7 @@
         <v>1.78</v>
       </c>
       <c r="Q82">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R82">
         <v>1.2</v>
@@ -21365,7 +21365,7 @@
         <v>1.01</v>
       </c>
       <c r="U82">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V82">
         <v>1.47</v>
@@ -21377,7 +21377,7 @@
         <v>1000</v>
       </c>
       <c r="Y82">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z82">
         <v>29</v>
@@ -21452,7 +21452,7 @@
         <v>1.01</v>
       </c>
       <c r="AX82">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY82">
         <v>7.8</v>
@@ -21562,22 +21562,22 @@
         <v>391</v>
       </c>
       <c r="F83">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="G83">
         <v>3.15</v>
       </c>
       <c r="H83">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="I83">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="J83">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="K83">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="L83">
         <v>1.33</v>
@@ -21586,16 +21586,16 @@
         <v>1.07</v>
       </c>
       <c r="N83">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="O83">
         <v>1.33</v>
       </c>
       <c r="P83">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="Q83">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="R83">
         <v>1.26</v>
@@ -21607,10 +21607,10 @@
         <v>1.01</v>
       </c>
       <c r="U83">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V83">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W83">
         <v>1.46</v>
@@ -21807,7 +21807,7 @@
         <v>6.6</v>
       </c>
       <c r="G84">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="H84">
         <v>1.47</v>
@@ -21828,7 +21828,7 @@
         <v>1.03</v>
       </c>
       <c r="N84">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="O84">
         <v>1.17</v>
@@ -21837,7 +21837,7 @@
         <v>2.44</v>
       </c>
       <c r="Q84">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R84">
         <v>1.57</v>
@@ -21846,7 +21846,7 @@
         <v>2.36</v>
       </c>
       <c r="T84">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U84">
         <v>1.94</v>
@@ -21855,7 +21855,7 @@
         <v>2.74</v>
       </c>
       <c r="W84">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X84">
         <v>1000</v>
@@ -22049,7 +22049,7 @@
         <v>2.18</v>
       </c>
       <c r="G85">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H85">
         <v>2.9</v>
@@ -22070,7 +22070,7 @@
         <v>1.01</v>
       </c>
       <c r="N85">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="O85">
         <v>1.13</v>
@@ -22097,7 +22097,7 @@
         <v>1.39</v>
       </c>
       <c r="W85">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X85">
         <v>1000</v>
@@ -22772,7 +22772,7 @@
         <v>396</v>
       </c>
       <c r="F88">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="G88">
         <v>5.6</v>
@@ -22784,10 +22784,10 @@
         <v>2.12</v>
       </c>
       <c r="J88">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="K88">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L88">
         <v>1.01</v>
@@ -23256,22 +23256,22 @@
         <v>398</v>
       </c>
       <c r="F90">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G90">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H90">
+        <v>2.52</v>
+      </c>
+      <c r="I90">
+        <v>3.45</v>
+      </c>
+      <c r="J90">
         <v>2.48</v>
       </c>
-      <c r="I90">
-        <v>3.55</v>
-      </c>
-      <c r="J90">
-        <v>2.62</v>
-      </c>
       <c r="K90">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L90">
         <v>1.01</v>
@@ -23280,22 +23280,22 @@
         <v>1.01</v>
       </c>
       <c r="N90">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="O90">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="P90">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Q90">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R90">
         <v>1.13</v>
       </c>
       <c r="S90">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="T90">
         <v>1.01</v>
@@ -23304,10 +23304,10 @@
         <v>1.01</v>
       </c>
       <c r="V90">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W90">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X90">
         <v>1000</v>
@@ -23421,7 +23421,7 @@
         <v>3.1</v>
       </c>
       <c r="BI90">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BJ90">
         <v>1000</v>
@@ -23782,7 +23782,7 @@
         <v>2.88</v>
       </c>
       <c r="T92">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U92">
         <v>1.49</v>
@@ -23985,13 +23985,13 @@
         <v>4.9</v>
       </c>
       <c r="G93">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H93">
         <v>1.74</v>
       </c>
       <c r="I93">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J93">
         <v>4.3</v>
@@ -24027,7 +24027,7 @@
         <v>1.66</v>
       </c>
       <c r="U93">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="V93">
         <v>2.3</v>
@@ -24138,7 +24138,7 @@
         <v>14</v>
       </c>
       <c r="BF93">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="BG93">
         <v>7.2</v>
@@ -24490,16 +24490,16 @@
         <v>1.02</v>
       </c>
       <c r="N95">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="O95">
         <v>1.13</v>
       </c>
       <c r="P95">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="Q95">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R95">
         <v>1.58</v>
@@ -24601,7 +24601,7 @@
         <v>6.4</v>
       </c>
       <c r="AY95">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AZ95">
         <v>14</v>
@@ -24625,7 +24625,7 @@
         <v>3</v>
       </c>
       <c r="BG95">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH95">
         <v>1000</v>
@@ -24708,22 +24708,22 @@
         <v>404</v>
       </c>
       <c r="F96">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="G96">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H96">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I96">
-        <v>10.5</v>
+        <v>990</v>
       </c>
       <c r="J96">
-        <v>3.95</v>
+        <v>1.06</v>
       </c>
       <c r="K96">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L96">
         <v>1.01</v>
@@ -24732,7 +24732,7 @@
         <v>1.01</v>
       </c>
       <c r="N96">
-        <v>3.85</v>
+        <v>2.14</v>
       </c>
       <c r="O96">
         <v>1.2</v>
@@ -24741,13 +24741,13 @@
         <v>2.14</v>
       </c>
       <c r="Q96">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="R96">
         <v>1.43</v>
       </c>
       <c r="S96">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T96">
         <v>1.11</v>
@@ -24774,7 +24774,7 @@
         <v>190</v>
       </c>
       <c r="AB96">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC96">
         <v>12.5</v>
@@ -24798,7 +24798,7 @@
         <v>85</v>
       </c>
       <c r="AJ96">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK96">
         <v>19.5</v>
@@ -24810,34 +24810,34 @@
         <v>120</v>
       </c>
       <c r="AN96">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO96">
         <v>100</v>
       </c>
       <c r="AP96">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ96">
         <v>17</v>
       </c>
       <c r="AR96">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS96">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT96">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU96">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV96">
         <v>17</v>
       </c>
       <c r="AW96">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX96">
         <v>7.8</v>
@@ -24846,10 +24846,10 @@
         <v>7.4</v>
       </c>
       <c r="AZ96">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA96">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB96">
         <v>11.5</v>
@@ -24858,16 +24858,16 @@
         <v>11.5</v>
       </c>
       <c r="BD96">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE96">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF96">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG96">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH96">
         <v>1000</v>
@@ -24965,7 +24965,7 @@
         <v>3.35</v>
       </c>
       <c r="K97">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L97">
         <v>1.3</v>
@@ -24983,7 +24983,7 @@
         <v>1.9</v>
       </c>
       <c r="Q97">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R97">
         <v>1.35</v>
@@ -25216,7 +25216,7 @@
         <v>1.05</v>
       </c>
       <c r="N98">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="O98">
         <v>1.3</v>
@@ -25700,7 +25700,7 @@
         <v>1.01</v>
       </c>
       <c r="N100">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="O100">
         <v>1.33</v>
@@ -25924,7 +25924,7 @@
         <v>4.1</v>
       </c>
       <c r="H101">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="I101">
         <v>2.52</v>
@@ -25957,7 +25957,7 @@
         <v>1.25</v>
       </c>
       <c r="S101">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="T101">
         <v>1.01</v>
@@ -25978,10 +25978,10 @@
         <v>11</v>
       </c>
       <c r="Z101">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA101">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB101">
         <v>1000</v>
@@ -25999,7 +25999,7 @@
         <v>1000</v>
       </c>
       <c r="AG101">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH101">
         <v>1000</v>
@@ -26441,10 +26441,10 @@
         <v>1.21</v>
       </c>
       <c r="S103">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T103">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="U103">
         <v>1.01</v>
@@ -26695,7 +26695,7 @@
         <v>1.31</v>
       </c>
       <c r="W104">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X104">
         <v>11</v>
@@ -26713,7 +26713,7 @@
         <v>8</v>
       </c>
       <c r="AC104">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD104">
         <v>17</v>
@@ -26827,7 +26827,7 @@
         <v>5.6</v>
       </c>
       <c r="BO104">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BP104">
         <v>20</v>
@@ -27155,7 +27155,7 @@
         <v>2.8</v>
       </c>
       <c r="O106">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P106">
         <v>1.58</v>
@@ -27654,7 +27654,7 @@
         <v>3</v>
       </c>
       <c r="T108">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U108">
         <v>1.98</v>
@@ -28099,37 +28099,37 @@
         <v>2.24</v>
       </c>
       <c r="G110">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H110">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="I110">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J110">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K110">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L110">
         <v>1.01</v>
       </c>
       <c r="M110">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N110">
         <v>3.1</v>
       </c>
       <c r="O110">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P110">
         <v>1.73</v>
       </c>
       <c r="Q110">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R110">
         <v>1.26</v>
@@ -28138,7 +28138,7 @@
         <v>4.1</v>
       </c>
       <c r="T110">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="U110">
         <v>1.94</v>
@@ -28341,19 +28341,19 @@
         <v>3.35</v>
       </c>
       <c r="G111">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H111">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I111">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J111">
         <v>3.65</v>
       </c>
       <c r="K111">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L111">
         <v>1.01</v>
@@ -28371,7 +28371,7 @@
         <v>1.99</v>
       </c>
       <c r="Q111">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R111">
         <v>1.38</v>
@@ -28383,10 +28383,10 @@
         <v>1.65</v>
       </c>
       <c r="U111">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V111">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W111">
         <v>1.4</v>
@@ -28404,7 +28404,7 @@
         <v>30</v>
       </c>
       <c r="AB111">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC111">
         <v>8.800000000000001</v>
@@ -28413,7 +28413,7 @@
         <v>12</v>
       </c>
       <c r="AE111">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF111">
         <v>27</v>
@@ -28434,7 +28434,7 @@
         <v>44</v>
       </c>
       <c r="AL111">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM111">
         <v>95</v>
@@ -28443,7 +28443,7 @@
         <v>38</v>
       </c>
       <c r="AO111">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP111">
         <v>13.5</v>
@@ -28485,13 +28485,13 @@
         <v>50</v>
       </c>
       <c r="BC111">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD111">
         <v>40</v>
       </c>
       <c r="BE111">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF111">
         <v>28</v>
@@ -28592,10 +28592,10 @@
         <v>4.9</v>
       </c>
       <c r="J112">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K112">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L112">
         <v>1.01</v>
@@ -28834,7 +28834,7 @@
         <v>3</v>
       </c>
       <c r="J113">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K113">
         <v>3.1</v>
@@ -28846,16 +28846,16 @@
         <v>1.14</v>
       </c>
       <c r="N113">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="O113">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="P113">
         <v>1.3</v>
       </c>
       <c r="Q113">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="R113">
         <v>1.12</v>
@@ -29064,13 +29064,13 @@
         <v>422</v>
       </c>
       <c r="F114">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G114">
         <v>5.3</v>
       </c>
       <c r="H114">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="I114">
         <v>1.94</v>
@@ -29106,7 +29106,7 @@
         <v>2.72</v>
       </c>
       <c r="T114">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U114">
         <v>1.01</v>
@@ -30516,7 +30516,7 @@
         <v>428</v>
       </c>
       <c r="F120">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="G120">
         <v>1.91</v>
@@ -30531,7 +30531,7 @@
         <v>3.9</v>
       </c>
       <c r="K120">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="L120">
         <v>1.01</v>
@@ -30764,7 +30764,7 @@
         <v>1.97</v>
       </c>
       <c r="H121">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I121">
         <v>6.6</v>
@@ -30773,7 +30773,7 @@
         <v>3.4</v>
       </c>
       <c r="K121">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L121">
         <v>1.01</v>
@@ -31027,7 +31027,7 @@
         <v>2.72</v>
       </c>
       <c r="O122">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P122">
         <v>1.59</v>
@@ -31039,7 +31039,7 @@
         <v>1.23</v>
       </c>
       <c r="S122">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T122">
         <v>1.11</v>
@@ -31242,7 +31242,7 @@
         <v>431</v>
       </c>
       <c r="F123">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="G123">
         <v>2.36</v>
@@ -31251,13 +31251,13 @@
         <v>3.25</v>
       </c>
       <c r="I123">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J123">
-        <v>3.5</v>
+        <v>1.08</v>
       </c>
       <c r="K123">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="L123">
         <v>1.27</v>
@@ -31290,7 +31290,7 @@
         <v>1.01</v>
       </c>
       <c r="V123">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W123">
         <v>1.73</v>
@@ -31487,16 +31487,16 @@
         <v>2.34</v>
       </c>
       <c r="G124">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="H124">
         <v>3</v>
       </c>
       <c r="I124">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J124">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="K124">
         <v>3.7</v>
@@ -31508,7 +31508,7 @@
         <v>1.05</v>
       </c>
       <c r="N124">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O124">
         <v>1.28</v>
@@ -31517,13 +31517,13 @@
         <v>2</v>
       </c>
       <c r="Q124">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="R124">
         <v>1.38</v>
       </c>
       <c r="S124">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T124">
         <v>1.01</v>
@@ -31532,10 +31532,10 @@
         <v>1.01</v>
       </c>
       <c r="V124">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W124">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="X124">
         <v>1000</v>
@@ -31968,22 +31968,22 @@
         <v>434</v>
       </c>
       <c r="F126">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="G126">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="H126">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="I126">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J126">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="K126">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L126">
         <v>1.01</v>
@@ -31992,22 +31992,22 @@
         <v>1.03</v>
       </c>
       <c r="N126">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O126">
         <v>1.17</v>
       </c>
       <c r="P126">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q126">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R126">
         <v>1.63</v>
       </c>
       <c r="S126">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T126">
         <v>1.89</v>
@@ -32016,118 +32016,118 @@
         <v>1.94</v>
       </c>
       <c r="V126">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W126">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="X126">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Y126">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Z126">
+        <v>90</v>
+      </c>
+      <c r="AA126">
+        <v>290</v>
+      </c>
+      <c r="AB126">
+        <v>12.5</v>
+      </c>
+      <c r="AC126">
+        <v>14</v>
+      </c>
+      <c r="AD126">
+        <v>34</v>
+      </c>
+      <c r="AE126">
+        <v>130</v>
+      </c>
+      <c r="AF126">
+        <v>10</v>
+      </c>
+      <c r="AG126">
+        <v>11.5</v>
+      </c>
+      <c r="AH126">
+        <v>26</v>
+      </c>
+      <c r="AI126">
+        <v>110</v>
+      </c>
+      <c r="AJ126">
+        <v>12.5</v>
+      </c>
+      <c r="AK126">
+        <v>15</v>
+      </c>
+      <c r="AL126">
+        <v>32</v>
+      </c>
+      <c r="AM126">
         <v>120</v>
       </c>
-      <c r="AA126">
-        <v>400</v>
-      </c>
-      <c r="AB126">
-        <v>13</v>
-      </c>
-      <c r="AC126">
-        <v>18</v>
-      </c>
-      <c r="AD126">
-        <v>46</v>
-      </c>
-      <c r="AE126">
-        <v>170</v>
-      </c>
-      <c r="AF126">
-        <v>11.5</v>
-      </c>
-      <c r="AG126">
-        <v>13</v>
-      </c>
-      <c r="AH126">
-        <v>34</v>
-      </c>
-      <c r="AI126">
-        <v>140</v>
-      </c>
-      <c r="AJ126">
-        <v>13.5</v>
-      </c>
-      <c r="AK126">
-        <v>17</v>
-      </c>
-      <c r="AL126">
-        <v>40</v>
-      </c>
-      <c r="AM126">
-        <v>160</v>
-      </c>
       <c r="AN126">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AO126">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AP126">
-        <v>3.95</v>
+        <v>23</v>
       </c>
       <c r="AQ126">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="AR126">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS126">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="AT126">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU126">
         <v>12</v>
       </c>
       <c r="AV126">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="AW126">
+        <v>8</v>
+      </c>
+      <c r="AX126">
+        <v>8.4</v>
+      </c>
+      <c r="AY126">
+        <v>9.4</v>
+      </c>
+      <c r="AZ126">
+        <v>21</v>
+      </c>
+      <c r="BA126">
+        <v>7.8</v>
+      </c>
+      <c r="BB126">
+        <v>10.5</v>
+      </c>
+      <c r="BC126">
+        <v>12</v>
+      </c>
+      <c r="BD126">
+        <v>6.6</v>
+      </c>
+      <c r="BE126">
+        <v>7.6</v>
+      </c>
+      <c r="BF126">
         <v>4.3</v>
       </c>
-      <c r="AX126">
-        <v>8</v>
-      </c>
-      <c r="AY126">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ126">
-        <v>3.9</v>
-      </c>
-      <c r="BA126">
-        <v>4.3</v>
-      </c>
-      <c r="BB126">
-        <v>9.6</v>
-      </c>
-      <c r="BC126">
-        <v>11.5</v>
-      </c>
-      <c r="BD126">
-        <v>4</v>
-      </c>
-      <c r="BE126">
-        <v>4.3</v>
-      </c>
-      <c r="BF126">
-        <v>4</v>
-      </c>
       <c r="BG126">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BH126">
         <v>1000</v>
@@ -32216,7 +32216,7 @@
         <v>110</v>
       </c>
       <c r="H127">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I127">
         <v>1000</v>
@@ -32234,7 +32234,7 @@
         <v>1.01</v>
       </c>
       <c r="N127">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O127">
         <v>1.09</v>
@@ -32261,7 +32261,7 @@
         <v>1.01</v>
       </c>
       <c r="W127">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X127">
         <v>1000</v>
@@ -32467,7 +32467,7 @@
         <v>3.5</v>
       </c>
       <c r="K128">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L128">
         <v>1.01</v>
@@ -32482,7 +32482,7 @@
         <v>1.36</v>
       </c>
       <c r="P128">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q128">
         <v>2.04</v>
@@ -32497,7 +32497,7 @@
         <v>1.75</v>
       </c>
       <c r="U128">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="V128">
         <v>1.23</v>
@@ -32524,7 +32524,7 @@
         <v>8.4</v>
       </c>
       <c r="AD128">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AE128">
         <v>85</v>
@@ -32566,7 +32566,7 @@
         <v>13.5</v>
       </c>
       <c r="AR128">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS128">
         <v>9</v>
@@ -32709,7 +32709,7 @@
         <v>3.5</v>
       </c>
       <c r="K129">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L129">
         <v>1.01</v>
@@ -32718,7 +32718,7 @@
         <v>1.08</v>
       </c>
       <c r="N129">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="O129">
         <v>1.33</v>
@@ -32727,7 +32727,7 @@
         <v>1.66</v>
       </c>
       <c r="Q129">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="R129">
         <v>1.26</v>
@@ -33184,7 +33184,7 @@
         <v>3.15</v>
       </c>
       <c r="H131">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="I131">
         <v>3.3</v>
@@ -33193,7 +33193,7 @@
         <v>3.2</v>
       </c>
       <c r="K131">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L131">
         <v>1.29</v>
@@ -33202,16 +33202,16 @@
         <v>1.01</v>
       </c>
       <c r="N131">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="O131">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P131">
         <v>1.83</v>
       </c>
       <c r="Q131">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R131">
         <v>1.31</v>
@@ -33462,7 +33462,7 @@
         <v>2.88</v>
       </c>
       <c r="T132">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U132">
         <v>1.74</v>
@@ -34146,22 +34146,22 @@
         <v>443</v>
       </c>
       <c r="F135">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="G135">
         <v>1.85</v>
       </c>
       <c r="H135">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="I135">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J135">
-        <v>1.06</v>
+        <v>3.85</v>
       </c>
       <c r="K135">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L135">
         <v>1.01</v>
@@ -34182,7 +34182,7 @@
         <v>1.68</v>
       </c>
       <c r="R135">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="S135">
         <v>2.66</v>
@@ -34415,7 +34415,7 @@
         <v>3</v>
       </c>
       <c r="O136">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P136">
         <v>1.53</v>
@@ -34675,7 +34675,7 @@
         <v>1.84</v>
       </c>
       <c r="U137">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V137">
         <v>1.17</v>
@@ -34699,22 +34699,22 @@
         <v>7.8</v>
       </c>
       <c r="AC137">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD137">
         <v>25</v>
       </c>
       <c r="AE137">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF137">
         <v>9.6</v>
       </c>
       <c r="AG137">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AH137">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI137">
         <v>120</v>
@@ -34747,7 +34747,7 @@
         <v>44</v>
       </c>
       <c r="AS137">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AT137">
         <v>7</v>
@@ -34759,7 +34759,7 @@
         <v>21</v>
       </c>
       <c r="AW137">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX137">
         <v>8.4</v>
@@ -34783,13 +34783,13 @@
         <v>34</v>
       </c>
       <c r="BE137">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF137">
         <v>9.800000000000001</v>
       </c>
       <c r="BG137">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH137">
         <v>1000</v>
@@ -34875,19 +34875,19 @@
         <v>1.76</v>
       </c>
       <c r="G138">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H138">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I138">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J138">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K138">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L138">
         <v>1.01</v>
@@ -34902,10 +34902,10 @@
         <v>1.35</v>
       </c>
       <c r="P138">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="Q138">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="R138">
         <v>1.24</v>
@@ -34923,13 +34923,13 @@
         <v>1.2</v>
       </c>
       <c r="W138">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X138">
         <v>1000</v>
       </c>
       <c r="Y138">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z138">
         <v>55</v>
@@ -34947,13 +34947,13 @@
         <v>29</v>
       </c>
       <c r="AE138">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF138">
         <v>1000</v>
       </c>
       <c r="AG138">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH138">
         <v>1000</v>
@@ -34962,7 +34962,7 @@
         <v>1000</v>
       </c>
       <c r="AJ138">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK138">
         <v>30</v>
@@ -34980,58 +34980,58 @@
         <v>1000</v>
       </c>
       <c r="AP138">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="AQ138">
-        <v>1.47</v>
+        <v>11</v>
       </c>
       <c r="AR138">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="AS138">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="AT138">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="AU138">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AV138">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AW138">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="AX138">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="AY138">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AZ138">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="BA138">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="BB138">
-        <v>1.47</v>
+        <v>14.5</v>
       </c>
       <c r="BC138">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="BD138">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="BE138">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="BF138">
         <v>9.199999999999999</v>
       </c>
       <c r="BG138">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="BH138">
         <v>1000</v>
@@ -35144,7 +35144,7 @@
         <v>1.31</v>
       </c>
       <c r="P139">
-        <v>1.26</v>
+        <v>1.89</v>
       </c>
       <c r="Q139">
         <v>1.94</v>
@@ -35607,7 +35607,7 @@
         <v>1.76</v>
       </c>
       <c r="I141">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="J141">
         <v>3.3</v>
@@ -35616,16 +35616,16 @@
         <v>4.7</v>
       </c>
       <c r="L141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P141">
         <v>1.74</v>
@@ -35634,10 +35634,10 @@
         <v>2</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S141">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T141">
         <v>1.01</v>
@@ -35646,10 +35646,10 @@
         <v>1.01</v>
       </c>
       <c r="V141">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W141">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X141">
         <v>15</v>
@@ -35760,64 +35760,64 @@
         <v>10.5</v>
       </c>
       <c r="BH141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA141">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB141" t="s">
         <v>450</v>
